--- a/Data_Timbulan_Sampah/Data_Timbulan_Sampah_SIPSN_KLHK_2023.xlsx
+++ b/Data_Timbulan_Sampah/Data_Timbulan_Sampah_SIPSN_KLHK_2023.xlsx
@@ -201,8 +201,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <cols>
     <col min="1" max="1" width="6.75" customWidth="1"/>
-    <col min="2" max="2" width="10.8" customWidth="1"/>
-    <col min="3" max="3" width="24.3" customWidth="1"/>
+    <col min="2" max="2" width="35.1" customWidth="1"/>
+    <col min="3" max="3" width="43.2" customWidth="1"/>
     <col min="4" max="4" width="36.45" customWidth="1"/>
     <col min="5" max="5" width="37.800000000000004" customWidth="1"/>
   </cols>
@@ -451,6 +451,8070 @@
         <v>19094.90</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B13">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C13">
+        <is>
+          <t xml:space="preserve">Kab. Bireuen</t>
+        </is>
+      </c>
+      <c r="D13" s="66">
+        <v>158.36</v>
+      </c>
+      <c r="E13" s="64">
+        <v>57800.09</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B14">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C14">
+        <is>
+          <t xml:space="preserve">Kab. Aceh Barat Daya</t>
+        </is>
+      </c>
+      <c r="D14" s="66">
+        <v>77.67</v>
+      </c>
+      <c r="E14" s="64">
+        <v>28348.09</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B15">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C15">
+        <is>
+          <t xml:space="preserve">Kab. Gayo Lues</t>
+        </is>
+      </c>
+      <c r="D15" s="66">
+        <v>41.28</v>
+      </c>
+      <c r="E15" s="64">
+        <v>15068.51</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C16">
+        <is>
+          <t xml:space="preserve">Kab. Aceh Jaya</t>
+        </is>
+      </c>
+      <c r="D16" s="66">
+        <v>48.01</v>
+      </c>
+      <c r="E16" s="64">
+        <v>17525.11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B17">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C17">
+        <is>
+          <t xml:space="preserve">Kab. Nagan Raya</t>
+        </is>
+      </c>
+      <c r="D17" s="66">
+        <v>69.73</v>
+      </c>
+      <c r="E17" s="64">
+        <v>25451.60</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B18">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C18">
+        <is>
+          <t xml:space="preserve">Kab. Aceh Tamiang</t>
+        </is>
+      </c>
+      <c r="D18" s="66">
+        <v>122.09</v>
+      </c>
+      <c r="E18" s="64">
+        <v>44561.68</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B19">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C19">
+        <is>
+          <t xml:space="preserve">Kab. Bener Meriah</t>
+        </is>
+      </c>
+      <c r="D19" s="66">
+        <v>67.63</v>
+      </c>
+      <c r="E19" s="64">
+        <v>24685.68</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B20">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C20">
+        <is>
+          <t xml:space="preserve">Kab. Pidie Jaya</t>
+        </is>
+      </c>
+      <c r="D20" s="66">
+        <v>81.05</v>
+      </c>
+      <c r="E20" s="64">
+        <v>29581.54</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B21">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C21">
+        <is>
+          <t xml:space="preserve">Kota Banda Aceh</t>
+        </is>
+      </c>
+      <c r="D21" s="66">
+        <v>255.81</v>
+      </c>
+      <c r="E21" s="64">
+        <v>93370.54</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B22">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C22">
+        <is>
+          <t xml:space="preserve">Kota Sabang</t>
+        </is>
+      </c>
+      <c r="D22" s="66">
+        <v>17.28</v>
+      </c>
+      <c r="E22" s="64">
+        <v>6308.37</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B23">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C23">
+        <is>
+          <t xml:space="preserve">Kota Lhokseumawe</t>
+        </is>
+      </c>
+      <c r="D23" s="66">
+        <v>98.06</v>
+      </c>
+      <c r="E23" s="64">
+        <v>35793.28</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B24">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C24">
+        <is>
+          <t xml:space="preserve">Kota Langsa</t>
+        </is>
+      </c>
+      <c r="D24" s="66">
+        <v>96.32</v>
+      </c>
+      <c r="E24" s="64">
+        <v>35154.98</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B25">
+        <is>
+          <t xml:space="preserve">Aceh</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C25">
+        <is>
+          <t xml:space="preserve">Kota Subulussalam</t>
+        </is>
+      </c>
+      <c r="D25" s="66">
+        <v>57.07</v>
+      </c>
+      <c r="E25" s="64">
+        <v>20831.06</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B26">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C26">
+        <is>
+          <t xml:space="preserve">Kab. Nias</t>
+        </is>
+      </c>
+      <c r="D26" s="66">
+        <v>58.76</v>
+      </c>
+      <c r="E26" s="64">
+        <v>21446.67</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B27">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C27">
+        <is>
+          <t xml:space="preserve">Kab. Langkat</t>
+        </is>
+      </c>
+      <c r="D27" s="66">
+        <v>521.55</v>
+      </c>
+      <c r="E27" s="64">
+        <v>190367.39</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B28">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C28">
+        <is>
+          <t xml:space="preserve">Kab. Deli Serdang</t>
+        </is>
+      </c>
+      <c r="D28" s="64">
+        <v>1126.61</v>
+      </c>
+      <c r="E28" s="64">
+        <v>411211.01</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B29">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C29">
+        <is>
+          <t xml:space="preserve">Kab. Simalungun</t>
+        </is>
+      </c>
+      <c r="D29" s="66">
+        <v>510.81</v>
+      </c>
+      <c r="E29" s="64">
+        <v>186444.74</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B30">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C30">
+        <is>
+          <t xml:space="preserve">Kab. Labuhanbatu</t>
+        </is>
+      </c>
+      <c r="D30" s="66">
+        <v>366.68</v>
+      </c>
+      <c r="E30" s="64">
+        <v>133837.54</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B31">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C31">
+        <is>
+          <t xml:space="preserve">Kab. Toba</t>
+        </is>
+      </c>
+      <c r="D31" s="66">
+        <v>111.02</v>
+      </c>
+      <c r="E31" s="64">
+        <v>40522.11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B32">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C32">
+        <is>
+          <t xml:space="preserve">Kab. Mandailing Natal</t>
+        </is>
+      </c>
+      <c r="D32" s="66">
+        <v>193.95</v>
+      </c>
+      <c r="E32" s="64">
+        <v>70791.60</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B33">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C33">
+        <is>
+          <t xml:space="preserve">Kab. Pakpak Bharat</t>
+        </is>
+      </c>
+      <c r="D33" s="66">
+        <v>21.84</v>
+      </c>
+      <c r="E33" s="64">
+        <v>7973.06</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B34">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C34">
+        <is>
+          <t xml:space="preserve">Kab. Humbang Hasundutan</t>
+        </is>
+      </c>
+      <c r="D34" s="66">
+        <v>61.41</v>
+      </c>
+      <c r="E34" s="64">
+        <v>22415.85</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B35">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C35">
+        <is>
+          <t xml:space="preserve">Kota Medan</t>
+        </is>
+      </c>
+      <c r="D35" s="64">
+        <v>1768.94</v>
+      </c>
+      <c r="E35" s="64">
+        <v>645661.28</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B36">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C36">
+        <is>
+          <t xml:space="preserve">Kota Pematangsiantar</t>
+        </is>
+      </c>
+      <c r="D36" s="66">
+        <v>160.73</v>
+      </c>
+      <c r="E36" s="64">
+        <v>58664.63</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B37">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C37">
+        <is>
+          <t xml:space="preserve">Kota Sibolga</t>
+        </is>
+      </c>
+      <c r="D37" s="66">
+        <v>39.49</v>
+      </c>
+      <c r="E37" s="64">
+        <v>14413.56</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B38">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C38">
+        <is>
+          <t xml:space="preserve">Kota Tebing Tinggi</t>
+        </is>
+      </c>
+      <c r="D38" s="66">
+        <v>126.39</v>
+      </c>
+      <c r="E38" s="64">
+        <v>46131.55</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B39">
+        <is>
+          <t xml:space="preserve">Sumatera Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C39">
+        <is>
+          <t xml:space="preserve">Kota Padangsidimpuan</t>
+        </is>
+      </c>
+      <c r="D39" s="66">
+        <v>165.35</v>
+      </c>
+      <c r="E39" s="64">
+        <v>60353.44</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B40">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C40">
+        <is>
+          <t xml:space="preserve">Kab. Pesisir Selatan</t>
+        </is>
+      </c>
+      <c r="D40" s="66">
+        <v>154.96</v>
+      </c>
+      <c r="E40" s="64">
+        <v>56558.72</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B41">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C41">
+        <is>
+          <t xml:space="preserve">Kab. Solok</t>
+        </is>
+      </c>
+      <c r="D41" s="66">
+        <v>162.28</v>
+      </c>
+      <c r="E41" s="64">
+        <v>59233.95</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B42">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C42">
+        <is>
+          <t xml:space="preserve">Kab. Sijunjung</t>
+        </is>
+      </c>
+      <c r="D42" s="66">
+        <v>99.92</v>
+      </c>
+      <c r="E42" s="64">
+        <v>36471.20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B43">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C43">
+        <is>
+          <t xml:space="preserve">Kab. Tanah Datar</t>
+        </is>
+      </c>
+      <c r="D43" s="66">
+        <v>129.82</v>
+      </c>
+      <c r="E43" s="64">
+        <v>47382.56</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B44">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C44">
+        <is>
+          <t xml:space="preserve">Kab. Padang Pariaman</t>
+        </is>
+      </c>
+      <c r="D44" s="66">
+        <v>218.06</v>
+      </c>
+      <c r="E44" s="64">
+        <v>79593.54</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B45">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C45">
+        <is>
+          <t xml:space="preserve">Kab. Agam</t>
+        </is>
+      </c>
+      <c r="D45" s="66">
+        <v>219.63</v>
+      </c>
+      <c r="E45" s="64">
+        <v>80163.78</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B46">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C46">
+        <is>
+          <t xml:space="preserve">Kab. Lima Puluh Kota</t>
+        </is>
+      </c>
+      <c r="D46" s="66">
+        <v>156.07</v>
+      </c>
+      <c r="E46" s="64">
+        <v>56964.67</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B47">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C47">
+        <is>
+          <t xml:space="preserve">Kab. Pasaman</t>
+        </is>
+      </c>
+      <c r="D47" s="66">
+        <v>122.97</v>
+      </c>
+      <c r="E47" s="64">
+        <v>44884.05</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B48">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C48">
+        <is>
+          <t xml:space="preserve">Kab. Dharmasraya</t>
+        </is>
+      </c>
+      <c r="D48" s="66">
+        <v>187.61</v>
+      </c>
+      <c r="E48" s="64">
+        <v>68476.63</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B49">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C49">
+        <is>
+          <t xml:space="preserve">Kab. Solok Selatan</t>
+        </is>
+      </c>
+      <c r="D49" s="66">
+        <v>75.46</v>
+      </c>
+      <c r="E49" s="64">
+        <v>27542.75</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B50">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C50">
+        <is>
+          <t xml:space="preserve">Kota Padang</t>
+        </is>
+      </c>
+      <c r="D50" s="66">
+        <v>647.39</v>
+      </c>
+      <c r="E50" s="64">
+        <v>236296.62</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B51">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C51">
+        <is>
+          <t xml:space="preserve">Kota Solok</t>
+        </is>
+      </c>
+      <c r="D51" s="66">
+        <v>55.79</v>
+      </c>
+      <c r="E51" s="64">
+        <v>20364.12</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B52">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C52">
+        <is>
+          <t xml:space="preserve">Kota Sawahlunto</t>
+        </is>
+      </c>
+      <c r="D52" s="66">
+        <v>18.98</v>
+      </c>
+      <c r="E52" s="64">
+        <v>6925.99</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B53">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C53">
+        <is>
+          <t xml:space="preserve">Kota Padang Panjang</t>
+        </is>
+      </c>
+      <c r="D53" s="66">
+        <v>49.25</v>
+      </c>
+      <c r="E53" s="64">
+        <v>17975.23</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B54">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C54">
+        <is>
+          <t xml:space="preserve">Kota Bukittinggi</t>
+        </is>
+      </c>
+      <c r="D54" s="66">
+        <v>129.42</v>
+      </c>
+      <c r="E54" s="64">
+        <v>47238.48</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B55">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C55">
+        <is>
+          <t xml:space="preserve">Kota Payakumbuh</t>
+        </is>
+      </c>
+      <c r="D55" s="66">
+        <v>93.26</v>
+      </c>
+      <c r="E55" s="64">
+        <v>34041.59</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B56">
+        <is>
+          <t xml:space="preserve">Sumatera Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C56">
+        <is>
+          <t xml:space="preserve">Kota Pariaman</t>
+        </is>
+      </c>
+      <c r="D56" s="66">
+        <v>39.79</v>
+      </c>
+      <c r="E56" s="64">
+        <v>14524.66</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B57">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C57">
+        <is>
+          <t xml:space="preserve">Kab. Indragiri Hulu</t>
+        </is>
+      </c>
+      <c r="D57" s="66">
+        <v>185.63</v>
+      </c>
+      <c r="E57" s="64">
+        <v>67755.68</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B58">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C58">
+        <is>
+          <t xml:space="preserve">Kab. Bengkalis</t>
+        </is>
+      </c>
+      <c r="D58" s="66">
+        <v>260.59</v>
+      </c>
+      <c r="E58" s="64">
+        <v>95114.96</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B59">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C59">
+        <is>
+          <t xml:space="preserve">Kab. Rokan Hulu</t>
+        </is>
+      </c>
+      <c r="D59" s="66">
+        <v>377.35</v>
+      </c>
+      <c r="E59" s="64">
+        <v>137732.69</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B60">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C60">
+        <is>
+          <t xml:space="preserve">Kab. Rokan Hilir</t>
+        </is>
+      </c>
+      <c r="D60" s="66">
+        <v>339.39</v>
+      </c>
+      <c r="E60" s="64">
+        <v>123878.45</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B61">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C61">
+        <is>
+          <t xml:space="preserve">Kab. Siak</t>
+        </is>
+      </c>
+      <c r="D61" s="66">
+        <v>191.02</v>
+      </c>
+      <c r="E61" s="64">
+        <v>69722.30</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B62">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C62">
+        <is>
+          <t xml:space="preserve">Kab. Kuantan Singingi</t>
+        </is>
+      </c>
+      <c r="D62" s="66">
+        <v>140.71</v>
+      </c>
+      <c r="E62" s="64">
+        <v>51360.76</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B63">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C63">
+        <is>
+          <t xml:space="preserve">Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="D63" s="64">
+        <v>1011.01</v>
+      </c>
+      <c r="E63" s="64">
+        <v>369019.82</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B64">
+        <is>
+          <t xml:space="preserve">Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C64">
+        <is>
+          <t xml:space="preserve">Kota Dumai</t>
+        </is>
+      </c>
+      <c r="D64" s="66">
+        <v>170.16</v>
+      </c>
+      <c r="E64" s="64">
+        <v>62106.58</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B65">
+        <is>
+          <t xml:space="preserve">Jambi</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C65">
+        <is>
+          <t xml:space="preserve">Kab. Bungo</t>
+        </is>
+      </c>
+      <c r="D65" s="66">
+        <v>161.68</v>
+      </c>
+      <c r="E65" s="64">
+        <v>59014.11</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B66">
+        <is>
+          <t xml:space="preserve">Jambi</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C66">
+        <is>
+          <t xml:space="preserve">Kab. Tebo</t>
+        </is>
+      </c>
+      <c r="D66" s="66">
+        <v>143.96</v>
+      </c>
+      <c r="E66" s="64">
+        <v>52546.28</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B67">
+        <is>
+          <t xml:space="preserve">Jambi</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C67">
+        <is>
+          <t xml:space="preserve">Kota Jambi</t>
+        </is>
+      </c>
+      <c r="D67" s="66">
+        <v>443.56</v>
+      </c>
+      <c r="E67" s="64">
+        <v>161897.58</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B68">
+        <is>
+          <t xml:space="preserve">Jambi</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C68">
+        <is>
+          <t xml:space="preserve">Kota Sungai Penuh</t>
+        </is>
+      </c>
+      <c r="D68" s="66">
+        <v>50.43</v>
+      </c>
+      <c r="E68" s="64">
+        <v>18405.31</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B69">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C69">
+        <is>
+          <t xml:space="preserve">Kab. Ogan Komering Ulu</t>
+        </is>
+      </c>
+      <c r="D69" s="66">
+        <v>152.00</v>
+      </c>
+      <c r="E69" s="64">
+        <v>55478.83</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B70">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C70">
+        <is>
+          <t xml:space="preserve">Kab. Muara Enim</t>
+        </is>
+      </c>
+      <c r="D70" s="66">
+        <v>232.80</v>
+      </c>
+      <c r="E70" s="64">
+        <v>84971.42</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B71">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C71">
+        <is>
+          <t xml:space="preserve">Kab. Lahat</t>
+        </is>
+      </c>
+      <c r="D71" s="66">
+        <v>268.64</v>
+      </c>
+      <c r="E71" s="64">
+        <v>98053.34</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B72">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C72">
+        <is>
+          <t xml:space="preserve">Kab. Musi Banyuasin</t>
+        </is>
+      </c>
+      <c r="D72" s="66">
+        <v>253.25</v>
+      </c>
+      <c r="E72" s="64">
+        <v>92436.10</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B73">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C73">
+        <is>
+          <t xml:space="preserve">Kab. Ogan Komering Ulu Timur</t>
+        </is>
+      </c>
+      <c r="D73" s="66">
+        <v>281.12</v>
+      </c>
+      <c r="E73" s="64">
+        <v>102609.82</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B74">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C74">
+        <is>
+          <t xml:space="preserve">Kab. Ogan Ilir</t>
+        </is>
+      </c>
+      <c r="D74" s="66">
+        <v>175.79</v>
+      </c>
+      <c r="E74" s="64">
+        <v>64162.47</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B75">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C75">
+        <is>
+          <t xml:space="preserve">Kab. Penukal Abab Lematang Ilir</t>
+        </is>
+      </c>
+      <c r="D75" s="66">
+        <v>104.89</v>
+      </c>
+      <c r="E75" s="64">
+        <v>38283.21</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B76">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C76">
+        <is>
+          <t xml:space="preserve">Kab. Musi Rawas Utara</t>
+        </is>
+      </c>
+      <c r="D76" s="66">
+        <v>77.80</v>
+      </c>
+      <c r="E76" s="64">
+        <v>28398.02</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B77">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C77">
+        <is>
+          <t xml:space="preserve">Kota Pagar Alam</t>
+        </is>
+      </c>
+      <c r="D77" s="66">
+        <v>73.92</v>
+      </c>
+      <c r="E77" s="64">
+        <v>26980.07</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B78">
+        <is>
+          <t xml:space="preserve">Sumatera Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C78">
+        <is>
+          <t xml:space="preserve">Kota Prabumulih</t>
+        </is>
+      </c>
+      <c r="D78" s="66">
+        <v>99.74</v>
+      </c>
+      <c r="E78" s="64">
+        <v>36405.83</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B79">
+        <is>
+          <t xml:space="preserve">Bengkulu</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C79">
+        <is>
+          <t xml:space="preserve">Kab. Rejang Lebong</t>
+        </is>
+      </c>
+      <c r="D79" s="66">
+        <v>198.54</v>
+      </c>
+      <c r="E79" s="64">
+        <v>72465.68</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B80">
+        <is>
+          <t xml:space="preserve">Bengkulu</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C80">
+        <is>
+          <t xml:space="preserve">Kab. Bengkulu Utara</t>
+        </is>
+      </c>
+      <c r="D80" s="66">
+        <v>181.12</v>
+      </c>
+      <c r="E80" s="64">
+        <v>66108.44</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B81">
+        <is>
+          <t xml:space="preserve">Bengkulu</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C81">
+        <is>
+          <t xml:space="preserve">Kab. Seluma</t>
+        </is>
+      </c>
+      <c r="D81" s="66">
+        <v>106.89</v>
+      </c>
+      <c r="E81" s="64">
+        <v>39013.94</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B82">
+        <is>
+          <t xml:space="preserve">Bengkulu</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C82">
+        <is>
+          <t xml:space="preserve">Kab. Lebong</t>
+        </is>
+      </c>
+      <c r="D82" s="66">
+        <v>83.61</v>
+      </c>
+      <c r="E82" s="64">
+        <v>30516.44</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B83">
+        <is>
+          <t xml:space="preserve">Bengkulu</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C83">
+        <is>
+          <t xml:space="preserve">Kab. Bengkulu Tengah</t>
+        </is>
+      </c>
+      <c r="D83" s="66">
+        <v>59.91</v>
+      </c>
+      <c r="E83" s="64">
+        <v>21866.06</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B84">
+        <is>
+          <t xml:space="preserve">Bengkulu</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C84">
+        <is>
+          <t xml:space="preserve">Kota Bengkulu</t>
+        </is>
+      </c>
+      <c r="D84" s="66">
+        <v>273.00</v>
+      </c>
+      <c r="E84" s="64">
+        <v>99645.77</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B85">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C85">
+        <is>
+          <t xml:space="preserve">Kab. Lampung Selatan</t>
+        </is>
+      </c>
+      <c r="D85" s="66">
+        <v>766.57</v>
+      </c>
+      <c r="E85" s="64">
+        <v>279799.58</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B86">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C86">
+        <is>
+          <t xml:space="preserve">Kab. Lampung Tengah</t>
+        </is>
+      </c>
+      <c r="D86" s="66">
+        <v>690.00</v>
+      </c>
+      <c r="E86" s="64">
+        <v>251850.93</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B87">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C87">
+        <is>
+          <t xml:space="preserve">Kab. Tulang Bawang</t>
+        </is>
+      </c>
+      <c r="D87" s="66">
+        <v>173.43</v>
+      </c>
+      <c r="E87" s="64">
+        <v>63300.93</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B88">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C88">
+        <is>
+          <t xml:space="preserve">Kab. Tanggamus</t>
+        </is>
+      </c>
+      <c r="D88" s="66">
+        <v>369.64</v>
+      </c>
+      <c r="E88" s="64">
+        <v>134920.35</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B89">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C89">
+        <is>
+          <t xml:space="preserve">Kab. Lampung Timur</t>
+        </is>
+      </c>
+      <c r="D89" s="66">
+        <v>568.72</v>
+      </c>
+      <c r="E89" s="64">
+        <v>207581.71</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B90">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C90">
+        <is>
+          <t xml:space="preserve">Kab. Way Kanan</t>
+        </is>
+      </c>
+      <c r="D90" s="66">
+        <v>193.55</v>
+      </c>
+      <c r="E90" s="64">
+        <v>70647.06</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B91">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C91">
+        <is>
+          <t xml:space="preserve">Kab. Pesawaran</t>
+        </is>
+      </c>
+      <c r="D91" s="66">
+        <v>194.27</v>
+      </c>
+      <c r="E91" s="64">
+        <v>70907.97</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B92">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C92">
+        <is>
+          <t xml:space="preserve">Kab. Pringsewu</t>
+        </is>
+      </c>
+      <c r="D92" s="66">
+        <v>163.37</v>
+      </c>
+      <c r="E92" s="64">
+        <v>59628.59</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B93">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C93">
+        <is>
+          <t xml:space="preserve">Kab. Tulang Bawang Barat</t>
+        </is>
+      </c>
+      <c r="D93" s="66">
+        <v>115.85</v>
+      </c>
+      <c r="E93" s="64">
+        <v>42284.52</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B94">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C94">
+        <is>
+          <t xml:space="preserve">Kab. Pesisir Barat</t>
+        </is>
+      </c>
+      <c r="D94" s="66">
+        <v>65.93</v>
+      </c>
+      <c r="E94" s="64">
+        <v>24063.14</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B95">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C95">
+        <is>
+          <t xml:space="preserve">Kota Bandar Lampung</t>
+        </is>
+      </c>
+      <c r="D95" s="66">
+        <v>786.46</v>
+      </c>
+      <c r="E95" s="64">
+        <v>287058.27</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B96">
+        <is>
+          <t xml:space="preserve">Lampung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C96">
+        <is>
+          <t xml:space="preserve">Kota Metro</t>
+        </is>
+      </c>
+      <c r="D96" s="66">
+        <v>105.67</v>
+      </c>
+      <c r="E96" s="64">
+        <v>38568.31</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B97">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C97">
+        <is>
+          <t xml:space="preserve">Kab. Bangka</t>
+        </is>
+      </c>
+      <c r="D97" s="66">
+        <v>136.41</v>
+      </c>
+      <c r="E97" s="64">
+        <v>49790.53</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B98">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C98">
+        <is>
+          <t xml:space="preserve">Kab. Belitung</t>
+        </is>
+      </c>
+      <c r="D98" s="66">
+        <v>75.08</v>
+      </c>
+      <c r="E98" s="64">
+        <v>27405.95</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B99">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C99">
+        <is>
+          <t xml:space="preserve">Kab. Bangka Selatan</t>
+        </is>
+      </c>
+      <c r="D99" s="66">
+        <v>84.14</v>
+      </c>
+      <c r="E99" s="64">
+        <v>30710.22</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B100">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C100">
+        <is>
+          <t xml:space="preserve">Kab. Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="D100" s="66">
+        <v>83.85</v>
+      </c>
+      <c r="E100" s="64">
+        <v>30604.52</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B101">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C101">
+        <is>
+          <t xml:space="preserve">Kab. Bangka Barat</t>
+        </is>
+      </c>
+      <c r="D101" s="66">
+        <v>83.92</v>
+      </c>
+      <c r="E101" s="64">
+        <v>30629.49</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B102">
+        <is>
+          <t xml:space="preserve">Kepulauan Bangka Belitung</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C102">
+        <is>
+          <t xml:space="preserve">Kab. Belitung Timur</t>
+        </is>
+      </c>
+      <c r="D102" s="66">
+        <v>52.52</v>
+      </c>
+      <c r="E102" s="64">
+        <v>19169.36</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B103">
+        <is>
+          <t xml:space="preserve">Kepulauan Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C103">
+        <is>
+          <t xml:space="preserve">Kab. Bintan</t>
+        </is>
+      </c>
+      <c r="D103" s="66">
+        <v>55.92</v>
+      </c>
+      <c r="E103" s="64">
+        <v>20409.89</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B104">
+        <is>
+          <t xml:space="preserve">Kepulauan Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C104">
+        <is>
+          <t xml:space="preserve">Kab. Karimun</t>
+        </is>
+      </c>
+      <c r="D104" s="66">
+        <v>182.42</v>
+      </c>
+      <c r="E104" s="64">
+        <v>66583.30</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B105">
+        <is>
+          <t xml:space="preserve">Kepulauan Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C105">
+        <is>
+          <t xml:space="preserve">Kab. Natuna</t>
+        </is>
+      </c>
+      <c r="D105" s="66">
+        <v>34.87</v>
+      </c>
+      <c r="E105" s="64">
+        <v>12725.80</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B106">
+        <is>
+          <t xml:space="preserve">Kepulauan Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C106">
+        <is>
+          <t xml:space="preserve">Kab. Kepulauan Anambas</t>
+        </is>
+      </c>
+      <c r="D106" s="66">
+        <v>13.36</v>
+      </c>
+      <c r="E106" s="64">
+        <v>4876.80</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B107">
+        <is>
+          <t xml:space="preserve">Kepulauan Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C107">
+        <is>
+          <t xml:space="preserve">Kota Batam</t>
+        </is>
+      </c>
+      <c r="D107" s="64">
+        <v>1159.05</v>
+      </c>
+      <c r="E107" s="64">
+        <v>423054.13</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B108">
+        <is>
+          <t xml:space="preserve">Kepulauan Riau</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C108">
+        <is>
+          <t xml:space="preserve">Kota Tanjung Pinang</t>
+        </is>
+      </c>
+      <c r="D108" s="66">
+        <v>152.65</v>
+      </c>
+      <c r="E108" s="64">
+        <v>55715.79</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B109">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C109">
+        <is>
+          <t xml:space="preserve">Kab. Adm. Kep. Seribu</t>
+        </is>
+      </c>
+      <c r="D109" s="66">
+        <v>18.18</v>
+      </c>
+      <c r="E109" s="64">
+        <v>6634.27</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B110">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C110">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Pusat</t>
+        </is>
+      </c>
+      <c r="D110" s="66">
+        <v>852.72</v>
+      </c>
+      <c r="E110" s="64">
+        <v>311242.80</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B111">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C111">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Utara</t>
+        </is>
+      </c>
+      <c r="D111" s="64">
+        <v>1382.36</v>
+      </c>
+      <c r="E111" s="64">
+        <v>504560.46</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B112">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C112">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Barat</t>
+        </is>
+      </c>
+      <c r="D112" s="64">
+        <v>2049.69</v>
+      </c>
+      <c r="E112" s="64">
+        <v>748135.30</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B113">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C113">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="D113" s="64">
+        <v>1971.13</v>
+      </c>
+      <c r="E113" s="64">
+        <v>719463.79</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B114">
+        <is>
+          <t xml:space="preserve">DKI Jakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C114">
+        <is>
+          <t xml:space="preserve">Kota Adm. Jakarta Timur</t>
+        </is>
+      </c>
+      <c r="D114" s="64">
+        <v>2333.19</v>
+      </c>
+      <c r="E114" s="64">
+        <v>851613.56</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B115">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C115">
+        <is>
+          <t xml:space="preserve">Kab. Bogor</t>
+        </is>
+      </c>
+      <c r="D115" s="64">
+        <v>2813.51</v>
+      </c>
+      <c r="E115" s="64">
+        <v>1026931.33</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B116">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C116">
+        <is>
+          <t xml:space="preserve">Kab. Cianjur</t>
+        </is>
+      </c>
+      <c r="D116" s="64">
+        <v>1267.50</v>
+      </c>
+      <c r="E116" s="64">
+        <v>462637.87</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B117">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C117">
+        <is>
+          <t xml:space="preserve">Kab. Bandung</t>
+        </is>
+      </c>
+      <c r="D117" s="64">
+        <v>1301.53</v>
+      </c>
+      <c r="E117" s="64">
+        <v>475058.82</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B118">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C118">
+        <is>
+          <t xml:space="preserve">Kab. Garut</t>
+        </is>
+      </c>
+      <c r="D118" s="64">
+        <v>1121.82</v>
+      </c>
+      <c r="E118" s="64">
+        <v>409465.37</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B119">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C119">
+        <is>
+          <t xml:space="preserve">Kab. Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="D119" s="66">
+        <v>705.33</v>
+      </c>
+      <c r="E119" s="64">
+        <v>257444.19</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B120">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C120">
+        <is>
+          <t xml:space="preserve">Kab. Ciamis</t>
+        </is>
+      </c>
+      <c r="D120" s="66">
+        <v>499.11</v>
+      </c>
+      <c r="E120" s="64">
+        <v>182174.42</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B121">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C121">
+        <is>
+          <t xml:space="preserve">Kab. Kuningan</t>
+        </is>
+      </c>
+      <c r="D121" s="66">
+        <v>599.41</v>
+      </c>
+      <c r="E121" s="64">
+        <v>218783.56</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B122">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C122">
+        <is>
+          <t xml:space="preserve">Kab. Cirebon</t>
+        </is>
+      </c>
+      <c r="D122" s="64">
+        <v>1274.64</v>
+      </c>
+      <c r="E122" s="64">
+        <v>465242.92</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B123">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C123">
+        <is>
+          <t xml:space="preserve">Kab. Sumedang</t>
+        </is>
+      </c>
+      <c r="D123" s="66">
+        <v>478.92</v>
+      </c>
+      <c r="E123" s="64">
+        <v>174806.09</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B124">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C124">
+        <is>
+          <t xml:space="preserve">Kab. Indramayu</t>
+        </is>
+      </c>
+      <c r="D124" s="64">
+        <v>1124.95</v>
+      </c>
+      <c r="E124" s="64">
+        <v>410606.17</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B125">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C125">
+        <is>
+          <t xml:space="preserve">Kab. Karawang</t>
+        </is>
+      </c>
+      <c r="D125" s="64">
+        <v>1254.92</v>
+      </c>
+      <c r="E125" s="64">
+        <v>458045.62</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B126">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C126">
+        <is>
+          <t xml:space="preserve">Kab. Bekasi</t>
+        </is>
+      </c>
+      <c r="D126" s="64">
+        <v>2219.00</v>
+      </c>
+      <c r="E126" s="64">
+        <v>809935.00</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B127">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C127">
+        <is>
+          <t xml:space="preserve">Kab. Bandung Barat</t>
+        </is>
+      </c>
+      <c r="D127" s="66">
+        <v>742.74</v>
+      </c>
+      <c r="E127" s="64">
+        <v>271099.81</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B128">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C128">
+        <is>
+          <t xml:space="preserve">Kab. Pangandaran</t>
+        </is>
+      </c>
+      <c r="D128" s="66">
+        <v>176.07</v>
+      </c>
+      <c r="E128" s="64">
+        <v>64265.84</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B129">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C129">
+        <is>
+          <t xml:space="preserve">Kota Bogor</t>
+        </is>
+      </c>
+      <c r="D129" s="66">
+        <v>779.81</v>
+      </c>
+      <c r="E129" s="64">
+        <v>284631.60</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B130">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C130">
+        <is>
+          <t xml:space="preserve">Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="D130" s="66">
+        <v>184.41</v>
+      </c>
+      <c r="E130" s="64">
+        <v>67308.30</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B131">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C131">
+        <is>
+          <t xml:space="preserve">Kota Bandung</t>
+        </is>
+      </c>
+      <c r="D131" s="64">
+        <v>1609.77</v>
+      </c>
+      <c r="E131" s="64">
+        <v>587565.25</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B132">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C132">
+        <is>
+          <t xml:space="preserve">Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="D132" s="66">
+        <v>212.84</v>
+      </c>
+      <c r="E132" s="64">
+        <v>77685.26</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B133">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C133">
+        <is>
+          <t xml:space="preserve">Kota Bekasi</t>
+        </is>
+      </c>
+      <c r="D133" s="64">
+        <v>1747.34</v>
+      </c>
+      <c r="E133" s="64">
+        <v>637778.59</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B134">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C134">
+        <is>
+          <t xml:space="preserve">Kota Depok</t>
+        </is>
+      </c>
+      <c r="D134" s="64">
+        <v>1265.79</v>
+      </c>
+      <c r="E134" s="64">
+        <v>462011.89</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B135">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C135">
+        <is>
+          <t xml:space="preserve">Kota Cimahi</t>
+        </is>
+      </c>
+      <c r="D135" s="66">
+        <v>230.21</v>
+      </c>
+      <c r="E135" s="64">
+        <v>84025.77</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B136">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C136">
+        <is>
+          <t xml:space="preserve">Kota Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="D136" s="66">
+        <v>323.17</v>
+      </c>
+      <c r="E136" s="64">
+        <v>117955.24</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B137">
+        <is>
+          <t xml:space="preserve">Jawa Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C137">
+        <is>
+          <t xml:space="preserve">Kota Banjar</t>
+        </is>
+      </c>
+      <c r="D137" s="66">
+        <v>86.64</v>
+      </c>
+      <c r="E137" s="64">
+        <v>31624.18</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B138">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C138">
+        <is>
+          <t xml:space="preserve">Kab. Cilacap</t>
+        </is>
+      </c>
+      <c r="D138" s="66">
+        <v>954.54</v>
+      </c>
+      <c r="E138" s="64">
+        <v>348406.57</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B139">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C139">
+        <is>
+          <t xml:space="preserve">Kab. Banyumas</t>
+        </is>
+      </c>
+      <c r="D139" s="66">
+        <v>541.80</v>
+      </c>
+      <c r="E139" s="64">
+        <v>197758.42</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B140">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C140">
+        <is>
+          <t xml:space="preserve">Kab. Kebumen</t>
+        </is>
+      </c>
+      <c r="D140" s="66">
+        <v>483.19</v>
+      </c>
+      <c r="E140" s="64">
+        <v>176363.85</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B141">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C141">
+        <is>
+          <t xml:space="preserve">Kab. Purworejo</t>
+        </is>
+      </c>
+      <c r="D141" s="66">
+        <v>321.73</v>
+      </c>
+      <c r="E141" s="64">
+        <v>117432.91</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B142">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C142">
+        <is>
+          <t xml:space="preserve">Kab. Wonosobo</t>
+        </is>
+      </c>
+      <c r="D142" s="66">
+        <v>363.87</v>
+      </c>
+      <c r="E142" s="64">
+        <v>132810.94</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B143">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C143">
+        <is>
+          <t xml:space="preserve">Kab. Magelang</t>
+        </is>
+      </c>
+      <c r="D143" s="66">
+        <v>662.38</v>
+      </c>
+      <c r="E143" s="64">
+        <v>241767.97</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B144">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C144">
+        <is>
+          <t xml:space="preserve">Kab. Boyolali</t>
+        </is>
+      </c>
+      <c r="D144" s="66">
+        <v>296.91</v>
+      </c>
+      <c r="E144" s="64">
+        <v>108373.66</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B145">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C145">
+        <is>
+          <t xml:space="preserve">Kab. Klaten</t>
+        </is>
+      </c>
+      <c r="D145" s="66">
+        <v>649.45</v>
+      </c>
+      <c r="E145" s="64">
+        <v>237050.70</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B146">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C146">
+        <is>
+          <t xml:space="preserve">Kab. Sukoharjo</t>
+        </is>
+      </c>
+      <c r="D146" s="66">
+        <v>364.70</v>
+      </c>
+      <c r="E146" s="64">
+        <v>133114.77</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B147">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C147">
+        <is>
+          <t xml:space="preserve">Kab. Wonogiri</t>
+        </is>
+      </c>
+      <c r="D147" s="66">
+        <v>350.68</v>
+      </c>
+      <c r="E147" s="64">
+        <v>127999.02</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B148">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C148">
+        <is>
+          <t xml:space="preserve">Kab. Karanganyar</t>
+        </is>
+      </c>
+      <c r="D148" s="66">
+        <v>380.31</v>
+      </c>
+      <c r="E148" s="64">
+        <v>138814.32</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B149">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C149">
+        <is>
+          <t xml:space="preserve">Kab. Sragen</t>
+        </is>
+      </c>
+      <c r="D149" s="66">
+        <v>595.35</v>
+      </c>
+      <c r="E149" s="64">
+        <v>217301.22</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B150">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C150">
+        <is>
+          <t xml:space="preserve">Kab. Grobogan</t>
+        </is>
+      </c>
+      <c r="D150" s="66">
+        <v>863.15</v>
+      </c>
+      <c r="E150" s="64">
+        <v>315050.32</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B151">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C151">
+        <is>
+          <t xml:space="preserve">Kab. Blora</t>
+        </is>
+      </c>
+      <c r="D151" s="66">
+        <v>387.49</v>
+      </c>
+      <c r="E151" s="64">
+        <v>141433.02</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B152">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C152">
+        <is>
+          <t xml:space="preserve">Kab. Rembang</t>
+        </is>
+      </c>
+      <c r="D152" s="66">
+        <v>254.16</v>
+      </c>
+      <c r="E152" s="64">
+        <v>92770.06</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B153">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C153">
+        <is>
+          <t xml:space="preserve">Kab. Pati</t>
+        </is>
+      </c>
+      <c r="D153" s="66">
+        <v>687.93</v>
+      </c>
+      <c r="E153" s="64">
+        <v>251092.63</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B154">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C154">
+        <is>
+          <t xml:space="preserve">Kab. Kudus</t>
+        </is>
+      </c>
+      <c r="D154" s="66">
+        <v>435.78</v>
+      </c>
+      <c r="E154" s="64">
+        <v>159061.34</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B155">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C155">
+        <is>
+          <t xml:space="preserve">Kab. Jepara</t>
+        </is>
+      </c>
+      <c r="D155" s="66">
+        <v>423.48</v>
+      </c>
+      <c r="E155" s="64">
+        <v>154571.51</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B156">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C156">
+        <is>
+          <t xml:space="preserve">Kab. Demak</t>
+        </is>
+      </c>
+      <c r="D156" s="66">
+        <v>733.93</v>
+      </c>
+      <c r="E156" s="64">
+        <v>267884.52</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B157">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C157">
+        <is>
+          <t xml:space="preserve">Kab. Semarang</t>
+        </is>
+      </c>
+      <c r="D157" s="66">
+        <v>533.16</v>
+      </c>
+      <c r="E157" s="64">
+        <v>194601.94</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B158">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C158">
+        <is>
+          <t xml:space="preserve">Kab. Temanggung</t>
+        </is>
+      </c>
+      <c r="D158" s="66">
+        <v>403.72</v>
+      </c>
+      <c r="E158" s="64">
+        <v>147357.80</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B159">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C159">
+        <is>
+          <t xml:space="preserve">Kab. Kendal</t>
+        </is>
+      </c>
+      <c r="D159" s="66">
+        <v>421.36</v>
+      </c>
+      <c r="E159" s="64">
+        <v>153796.40</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B160">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C160">
+        <is>
+          <t xml:space="preserve">Kab. Pekalongan</t>
+        </is>
+      </c>
+      <c r="D160" s="66">
+        <v>394.58</v>
+      </c>
+      <c r="E160" s="64">
+        <v>144022.43</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B161">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C161">
+        <is>
+          <t xml:space="preserve">Kab. Pemalang</t>
+        </is>
+      </c>
+      <c r="D161" s="66">
+        <v>600.30</v>
+      </c>
+      <c r="E161" s="64">
+        <v>219110.08</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B162">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C162">
+        <is>
+          <t xml:space="preserve">Kab. Tegal</t>
+        </is>
+      </c>
+      <c r="D162" s="66">
+        <v>604.09</v>
+      </c>
+      <c r="E162" s="64">
+        <v>220493.69</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B163">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C163">
+        <is>
+          <t xml:space="preserve">Kab. Brebes</t>
+        </is>
+      </c>
+      <c r="D163" s="64">
+        <v>1005.31</v>
+      </c>
+      <c r="E163" s="64">
+        <v>366937.60</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B164">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C164">
+        <is>
+          <t xml:space="preserve">Kota Magelang</t>
+        </is>
+      </c>
+      <c r="D164" s="66">
+        <v>80.55</v>
+      </c>
+      <c r="E164" s="64">
+        <v>29400.33</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B165">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C165">
+        <is>
+          <t xml:space="preserve">Kota Surakarta</t>
+        </is>
+      </c>
+      <c r="D165" s="66">
+        <v>419.11</v>
+      </c>
+      <c r="E165" s="64">
+        <v>152974.67</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B166">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C166">
+        <is>
+          <t xml:space="preserve">Kota Salatiga</t>
+        </is>
+      </c>
+      <c r="D166" s="66">
+        <v>116.43</v>
+      </c>
+      <c r="E166" s="64">
+        <v>42496.23</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B167">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C167">
+        <is>
+          <t xml:space="preserve">Kota Semarang</t>
+        </is>
+      </c>
+      <c r="D167" s="64">
+        <v>1182.29</v>
+      </c>
+      <c r="E167" s="64">
+        <v>431534.65</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B168">
+        <is>
+          <t xml:space="preserve">Jawa Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C168">
+        <is>
+          <t xml:space="preserve">Kota Tegal</t>
+        </is>
+      </c>
+      <c r="D168" s="66">
+        <v>187.13</v>
+      </c>
+      <c r="E168" s="64">
+        <v>68300.63</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B169">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C169">
+        <is>
+          <t xml:space="preserve">Kab. Kulon Progo</t>
+        </is>
+      </c>
+      <c r="D169" s="66">
+        <v>219.27</v>
+      </c>
+      <c r="E169" s="64">
+        <v>80033.90</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B170">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C170">
+        <is>
+          <t xml:space="preserve">Kab. Bantul</t>
+        </is>
+      </c>
+      <c r="D170" s="66">
+        <v>444.15</v>
+      </c>
+      <c r="E170" s="64">
+        <v>162114.46</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B171">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C171">
+        <is>
+          <t xml:space="preserve">Kab. Gunungkidul</t>
+        </is>
+      </c>
+      <c r="D171" s="66">
+        <v>385.15</v>
+      </c>
+      <c r="E171" s="64">
+        <v>140580.21</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B172">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C172">
+        <is>
+          <t xml:space="preserve">Kab. Sleman</t>
+        </is>
+      </c>
+      <c r="D172" s="66">
+        <v>601.79</v>
+      </c>
+      <c r="E172" s="64">
+        <v>219653.64</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B173">
+        <is>
+          <t xml:space="preserve">Daerah Istimewa Yogyakarta</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C173">
+        <is>
+          <t xml:space="preserve">Kota Yogyakarta</t>
+        </is>
+      </c>
+      <c r="D173" s="66">
+        <v>300.56</v>
+      </c>
+      <c r="E173" s="64">
+        <v>109704.11</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B174">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C174">
+        <is>
+          <t xml:space="preserve">Kab. Pacitan</t>
+        </is>
+      </c>
+      <c r="D174" s="66">
+        <v>288.62</v>
+      </c>
+      <c r="E174" s="64">
+        <v>105345.64</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B175">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C175">
+        <is>
+          <t xml:space="preserve">Kab. Ponorogo</t>
+        </is>
+      </c>
+      <c r="D175" s="66">
+        <v>385.70</v>
+      </c>
+      <c r="E175" s="64">
+        <v>140780.94</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B176">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C176">
+        <is>
+          <t xml:space="preserve">Kab. Trenggalek</t>
+        </is>
+      </c>
+      <c r="D176" s="66">
+        <v>300.43</v>
+      </c>
+      <c r="E176" s="64">
+        <v>109657.53</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B177">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C177">
+        <is>
+          <t xml:space="preserve">Kab. Tulungagung</t>
+        </is>
+      </c>
+      <c r="D177" s="66">
+        <v>558.98</v>
+      </c>
+      <c r="E177" s="64">
+        <v>204028.80</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B178">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C178">
+        <is>
+          <t xml:space="preserve">Kab. Blitar</t>
+        </is>
+      </c>
+      <c r="D178" s="66">
+        <v>413.67</v>
+      </c>
+      <c r="E178" s="64">
+        <v>150990.10</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B179">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C179">
+        <is>
+          <t xml:space="preserve">Kab. Kediri</t>
+        </is>
+      </c>
+      <c r="D179" s="66">
+        <v>662.41</v>
+      </c>
+      <c r="E179" s="64">
+        <v>241778.92</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B180">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C180">
+        <is>
+          <t xml:space="preserve">Kab. Malang</t>
+        </is>
+      </c>
+      <c r="D180" s="66">
+        <v>966.92</v>
+      </c>
+      <c r="E180" s="64">
+        <v>352927.26</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B181">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C181">
+        <is>
+          <t xml:space="preserve">Kab. Lumajang</t>
+        </is>
+      </c>
+      <c r="D181" s="66">
+        <v>535.00</v>
+      </c>
+      <c r="E181" s="64">
+        <v>195275.12</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B182">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C182">
+        <is>
+          <t xml:space="preserve">Kab. Jember</t>
+        </is>
+      </c>
+      <c r="D182" s="64">
+        <v>1033.69</v>
+      </c>
+      <c r="E182" s="64">
+        <v>377298.02</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B183">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C183">
+        <is>
+          <t xml:space="preserve">Kab. Banyuwangi</t>
+        </is>
+      </c>
+      <c r="D183" s="66">
+        <v>836.47</v>
+      </c>
+      <c r="E183" s="64">
+        <v>305312.85</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B184">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C184">
+        <is>
+          <t xml:space="preserve">Kab. Situbondo</t>
+        </is>
+      </c>
+      <c r="D184" s="66">
+        <v>252.41</v>
+      </c>
+      <c r="E184" s="64">
+        <v>92130.84</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B185">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C185">
+        <is>
+          <t xml:space="preserve">Kab. Sidoarjo</t>
+        </is>
+      </c>
+      <c r="D185" s="66">
+        <v>878.60</v>
+      </c>
+      <c r="E185" s="64">
+        <v>320690.10</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B186">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C186">
+        <is>
+          <t xml:space="preserve">Kab. Mojokerto</t>
+        </is>
+      </c>
+      <c r="D186" s="66">
+        <v>473.93</v>
+      </c>
+      <c r="E186" s="64">
+        <v>172984.00</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B187">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C187">
+        <is>
+          <t xml:space="preserve">Kab. Jombang</t>
+        </is>
+      </c>
+      <c r="D187" s="66">
+        <v>530.37</v>
+      </c>
+      <c r="E187" s="64">
+        <v>193583.44</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B188">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C188">
+        <is>
+          <t xml:space="preserve">Kab. Nganjuk</t>
+        </is>
+      </c>
+      <c r="D188" s="66">
+        <v>446.81</v>
+      </c>
+      <c r="E188" s="64">
+        <v>163086.82</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B189">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C189">
+        <is>
+          <t xml:space="preserve">Kab. Madiun</t>
+        </is>
+      </c>
+      <c r="D189" s="66">
+        <v>299.04</v>
+      </c>
+      <c r="E189" s="64">
+        <v>109147.99</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B190">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C190">
+        <is>
+          <t xml:space="preserve">Kab. Magetan</t>
+        </is>
+      </c>
+      <c r="D190" s="66">
+        <v>275.96</v>
+      </c>
+      <c r="E190" s="64">
+        <v>100725.11</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B191">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C191">
+        <is>
+          <t xml:space="preserve">Kab. Ngawi</t>
+        </is>
+      </c>
+      <c r="D191" s="66">
+        <v>370.68</v>
+      </c>
+      <c r="E191" s="64">
+        <v>135297.67</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B192">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C192">
+        <is>
+          <t xml:space="preserve">Kab. Bojonegoro</t>
+        </is>
+      </c>
+      <c r="D192" s="66">
+        <v>366.14</v>
+      </c>
+      <c r="E192" s="64">
+        <v>133639.42</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B193">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C193">
+        <is>
+          <t xml:space="preserve">Kab. Tuban</t>
+        </is>
+      </c>
+      <c r="D193" s="66">
+        <v>508.01</v>
+      </c>
+      <c r="E193" s="64">
+        <v>185422.94</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B194">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C194">
+        <is>
+          <t xml:space="preserve">Kab. Lamongan</t>
+        </is>
+      </c>
+      <c r="D194" s="66">
+        <v>552.57</v>
+      </c>
+      <c r="E194" s="64">
+        <v>201686.44</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B195">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C195">
+        <is>
+          <t xml:space="preserve">Kab. Gresik</t>
+        </is>
+      </c>
+      <c r="D195" s="66">
+        <v>395.17</v>
+      </c>
+      <c r="E195" s="64">
+        <v>144238.33</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B196">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C196">
+        <is>
+          <t xml:space="preserve">Kab. Bangkalan</t>
+        </is>
+      </c>
+      <c r="D196" s="66">
+        <v>417.15</v>
+      </c>
+      <c r="E196" s="64">
+        <v>152259.02</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B197">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C197">
+        <is>
+          <t xml:space="preserve">Kab. Sampang</t>
+        </is>
+      </c>
+      <c r="D197" s="66">
+        <v>464.41</v>
+      </c>
+      <c r="E197" s="64">
+        <v>169511.29</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B198">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C198">
+        <is>
+          <t xml:space="preserve">Kab. Pamekasan</t>
+        </is>
+      </c>
+      <c r="D198" s="66">
+        <v>277.14</v>
+      </c>
+      <c r="E198" s="64">
+        <v>101156.10</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B199">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C199">
+        <is>
+          <t xml:space="preserve">Kab. Sumenep</t>
+        </is>
+      </c>
+      <c r="D199" s="66">
+        <v>367.44</v>
+      </c>
+      <c r="E199" s="64">
+        <v>134116.66</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B200">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C200">
+        <is>
+          <t xml:space="preserve">Kota Kediri</t>
+        </is>
+      </c>
+      <c r="D200" s="66">
+        <v>173.87</v>
+      </c>
+      <c r="E200" s="64">
+        <v>63461.92</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B201">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C201">
+        <is>
+          <t xml:space="preserve">Kota Blitar</t>
+        </is>
+      </c>
+      <c r="D201" s="66">
+        <v>76.68</v>
+      </c>
+      <c r="E201" s="64">
+        <v>27988.20</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B202">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C202">
+        <is>
+          <t xml:space="preserve">Kota Malang</t>
+        </is>
+      </c>
+      <c r="D202" s="66">
+        <v>778.34</v>
+      </c>
+      <c r="E202" s="64">
+        <v>284095.41</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B203">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C203">
+        <is>
+          <t xml:space="preserve">Kota Probolinggo</t>
+        </is>
+      </c>
+      <c r="D203" s="66">
+        <v>97.82</v>
+      </c>
+      <c r="E203" s="64">
+        <v>35705.61</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B204">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C204">
+        <is>
+          <t xml:space="preserve">Kota Pasuruan</t>
+        </is>
+      </c>
+      <c r="D204" s="66">
+        <v>147.48</v>
+      </c>
+      <c r="E204" s="64">
+        <v>53830.17</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B205">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C205">
+        <is>
+          <t xml:space="preserve">Kota Mojokerto</t>
+        </is>
+      </c>
+      <c r="D205" s="66">
+        <v>98.31</v>
+      </c>
+      <c r="E205" s="64">
+        <v>35882.93</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B206">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C206">
+        <is>
+          <t xml:space="preserve">Kota Madiun</t>
+        </is>
+      </c>
+      <c r="D206" s="66">
+        <v>122.60</v>
+      </c>
+      <c r="E206" s="64">
+        <v>44750.39</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B207">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C207">
+        <is>
+          <t xml:space="preserve">Kota Surabaya</t>
+        </is>
+      </c>
+      <c r="D207" s="64">
+        <v>1800.05</v>
+      </c>
+      <c r="E207" s="64">
+        <v>657016.64</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B208">
+        <is>
+          <t xml:space="preserve">Jawa Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C208">
+        <is>
+          <t xml:space="preserve">Kota Batu</t>
+        </is>
+      </c>
+      <c r="D208" s="66">
+        <v>142.64</v>
+      </c>
+      <c r="E208" s="64">
+        <v>52062.68</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B209">
+        <is>
+          <t xml:space="preserve">Banten</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C209">
+        <is>
+          <t xml:space="preserve">Kab. Pandeglang</t>
+        </is>
+      </c>
+      <c r="D209" s="66">
+        <v>509.07</v>
+      </c>
+      <c r="E209" s="64">
+        <v>185812.30</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B210">
+        <is>
+          <t xml:space="preserve">Banten</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C210">
+        <is>
+          <t xml:space="preserve">Kab. Lebak</t>
+        </is>
+      </c>
+      <c r="D210" s="66">
+        <v>597.99</v>
+      </c>
+      <c r="E210" s="64">
+        <v>218266.50</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B211">
+        <is>
+          <t xml:space="preserve">Banten</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C211">
+        <is>
+          <t xml:space="preserve">Kab. Serang</t>
+        </is>
+      </c>
+      <c r="D211" s="64">
+        <v>1175.24</v>
+      </c>
+      <c r="E211" s="64">
+        <v>428962.78</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B212">
+        <is>
+          <t xml:space="preserve">Banten</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C212">
+        <is>
+          <t xml:space="preserve">Kota Tangerang</t>
+        </is>
+      </c>
+      <c r="D212" s="64">
+        <v>1409.53</v>
+      </c>
+      <c r="E212" s="64">
+        <v>514478.12</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B213">
+        <is>
+          <t xml:space="preserve">Banten</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C213">
+        <is>
+          <t xml:space="preserve">Kota Cilegon</t>
+        </is>
+      </c>
+      <c r="D213" s="66">
+        <v>278.83</v>
+      </c>
+      <c r="E213" s="64">
+        <v>101772.80</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B214">
+        <is>
+          <t xml:space="preserve">Banten</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C214">
+        <is>
+          <t xml:space="preserve">Kota Serang</t>
+        </is>
+      </c>
+      <c r="D214" s="66">
+        <v>601.38</v>
+      </c>
+      <c r="E214" s="64">
+        <v>219503.03</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B215">
+        <is>
+          <t xml:space="preserve">Banten</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C215">
+        <is>
+          <t xml:space="preserve">Kota Tangerang Selatan</t>
+        </is>
+      </c>
+      <c r="D215" s="64">
+        <v>1011.45</v>
+      </c>
+      <c r="E215" s="64">
+        <v>369177.50</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B216">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C216">
+        <is>
+          <t xml:space="preserve">Kab. Jembrana</t>
+        </is>
+      </c>
+      <c r="D216" s="66">
+        <v>163.74</v>
+      </c>
+      <c r="E216" s="64">
+        <v>59765.28</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B217">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C217">
+        <is>
+          <t xml:space="preserve">Kab. Tabanan</t>
+        </is>
+      </c>
+      <c r="D217" s="66">
+        <v>232.67</v>
+      </c>
+      <c r="E217" s="64">
+        <v>84922.73</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B218">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C218">
+        <is>
+          <t xml:space="preserve">Kab. Badung</t>
+        </is>
+      </c>
+      <c r="D218" s="66">
+        <v>534.86</v>
+      </c>
+      <c r="E218" s="64">
+        <v>195222.49</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B219">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C219">
+        <is>
+          <t xml:space="preserve">Kab. Gianyar</t>
+        </is>
+      </c>
+      <c r="D219" s="66">
+        <v>538.90</v>
+      </c>
+      <c r="E219" s="64">
+        <v>196698.50</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B220">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C220">
+        <is>
+          <t xml:space="preserve">Kab. Klungkung</t>
+        </is>
+      </c>
+      <c r="D220" s="66">
+        <v>110.25</v>
+      </c>
+      <c r="E220" s="64">
+        <v>40239.61</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B221">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C221">
+        <is>
+          <t xml:space="preserve">Kab. Bangli</t>
+        </is>
+      </c>
+      <c r="D221" s="66">
+        <v>112.86</v>
+      </c>
+      <c r="E221" s="64">
+        <v>41195.36</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B222">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C222">
+        <is>
+          <t xml:space="preserve">Kab. Karangasem</t>
+        </is>
+      </c>
+      <c r="D222" s="66">
+        <v>281.22</v>
+      </c>
+      <c r="E222" s="64">
+        <v>102643.48</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B223">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C223">
+        <is>
+          <t xml:space="preserve">Kab. Buleleng</t>
+        </is>
+      </c>
+      <c r="D223" s="66">
+        <v>412.50</v>
+      </c>
+      <c r="E223" s="64">
+        <v>150562.50</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B224">
+        <is>
+          <t xml:space="preserve">Bali</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C224">
+        <is>
+          <t xml:space="preserve">Kota Denpasar</t>
+        </is>
+      </c>
+      <c r="D224" s="66">
+        <v>980.78</v>
+      </c>
+      <c r="E224" s="64">
+        <v>357984.70</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B225">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C225">
+        <is>
+          <t xml:space="preserve">Kab. Lombok Barat</t>
+        </is>
+      </c>
+      <c r="D225" s="66">
+        <v>297.72</v>
+      </c>
+      <c r="E225" s="64">
+        <v>108669.11</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B226">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C226">
+        <is>
+          <t xml:space="preserve">Kab. Lombok Tengah</t>
+        </is>
+      </c>
+      <c r="D226" s="66">
+        <v>427.07</v>
+      </c>
+      <c r="E226" s="64">
+        <v>155881.57</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B227">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C227">
+        <is>
+          <t xml:space="preserve">Kab. Sumbawa</t>
+        </is>
+      </c>
+      <c r="D227" s="66">
+        <v>260.93</v>
+      </c>
+      <c r="E227" s="64">
+        <v>95239.63</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B228">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C228">
+        <is>
+          <t xml:space="preserve">Kota Mataram</t>
+        </is>
+      </c>
+      <c r="D228" s="66">
+        <v>271.69</v>
+      </c>
+      <c r="E228" s="64">
+        <v>99165.83</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B229">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C229">
+        <is>
+          <t xml:space="preserve">Kab. Kupang</t>
+        </is>
+      </c>
+      <c r="D229" s="66">
+        <v>154.89</v>
+      </c>
+      <c r="E229" s="64">
+        <v>56533.68</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B230">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C230">
+        <is>
+          <t xml:space="preserve">Kab. Timor Tengah Utara</t>
+        </is>
+      </c>
+      <c r="D230" s="66">
+        <v>107.23</v>
+      </c>
+      <c r="E230" s="64">
+        <v>39137.78</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B231">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C231">
+        <is>
+          <t xml:space="preserve">Kab. Belu</t>
+        </is>
+      </c>
+      <c r="D231" s="66">
+        <v>115.50</v>
+      </c>
+      <c r="E231" s="64">
+        <v>42158.96</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B232">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C232">
+        <is>
+          <t xml:space="preserve">Kab. Flores Timur</t>
+        </is>
+      </c>
+      <c r="D232" s="66">
+        <v>202.57</v>
+      </c>
+      <c r="E232" s="64">
+        <v>73936.59</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B233">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C233">
+        <is>
+          <t xml:space="preserve">Kab. Sikka</t>
+        </is>
+      </c>
+      <c r="D233" s="66">
+        <v>134.14</v>
+      </c>
+      <c r="E233" s="64">
+        <v>48962.56</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B234">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C234">
+        <is>
+          <t xml:space="preserve">Kab. Ngada</t>
+        </is>
+      </c>
+      <c r="D234" s="66">
+        <v>117.18</v>
+      </c>
+      <c r="E234" s="64">
+        <v>42769.68</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B235">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C235">
+        <is>
+          <t xml:space="preserve">Kab. Sumba Timur</t>
+        </is>
+      </c>
+      <c r="D235" s="66">
+        <v>59.71</v>
+      </c>
+      <c r="E235" s="64">
+        <v>21792.78</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B236">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C236">
+        <is>
+          <t xml:space="preserve">Kab. Lembata</t>
+        </is>
+      </c>
+      <c r="D236" s="66">
+        <v>88.37</v>
+      </c>
+      <c r="E236" s="64">
+        <v>32254.82</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B237">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C237">
+        <is>
+          <t xml:space="preserve">Kab. Rote Ndao</t>
+        </is>
+      </c>
+      <c r="D237" s="66">
+        <v>133.75</v>
+      </c>
+      <c r="E237" s="64">
+        <v>48819.44</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B238">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C238">
+        <is>
+          <t xml:space="preserve">Kab. Manggarai Barat</t>
+        </is>
+      </c>
+      <c r="D238" s="66">
+        <v>111.27</v>
+      </c>
+      <c r="E238" s="64">
+        <v>40614.86</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B239">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C239">
+        <is>
+          <t xml:space="preserve">Kab. Nagekeo</t>
+        </is>
+      </c>
+      <c r="D239" s="66">
+        <v>66.79</v>
+      </c>
+      <c r="E239" s="64">
+        <v>24377.33</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B240">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C240">
+        <is>
+          <t xml:space="preserve">Kab. Sumba Tengah</t>
+        </is>
+      </c>
+      <c r="D240" s="66">
+        <v>27.14</v>
+      </c>
+      <c r="E240" s="64">
+        <v>9907.78</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B241">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C241">
+        <is>
+          <t xml:space="preserve">Kab. Sumba Barat Daya</t>
+        </is>
+      </c>
+      <c r="D241" s="66">
+        <v>128.83</v>
+      </c>
+      <c r="E241" s="64">
+        <v>47022.66</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B242">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C242">
+        <is>
+          <t xml:space="preserve">Kab. Malaka</t>
+        </is>
+      </c>
+      <c r="D242" s="66">
+        <v>78.82</v>
+      </c>
+      <c r="E242" s="64">
+        <v>28769.88</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B243">
+        <is>
+          <t xml:space="preserve">Nusa Tenggara Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C243">
+        <is>
+          <t xml:space="preserve">Kota Kupang</t>
+        </is>
+      </c>
+      <c r="D243" s="66">
+        <v>234.46</v>
+      </c>
+      <c r="E243" s="64">
+        <v>85576.62</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B244">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C244">
+        <is>
+          <t xml:space="preserve">Kab. Sambas</t>
+        </is>
+      </c>
+      <c r="D244" s="66">
+        <v>322.09</v>
+      </c>
+      <c r="E244" s="64">
+        <v>117563.03</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B245">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C245">
+        <is>
+          <t xml:space="preserve">Kab. Mempawah</t>
+        </is>
+      </c>
+      <c r="D245" s="66">
+        <v>84.30</v>
+      </c>
+      <c r="E245" s="64">
+        <v>30769.28</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B246">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C246">
+        <is>
+          <t xml:space="preserve">Kab. Sanggau</t>
+        </is>
+      </c>
+      <c r="D246" s="66">
+        <v>249.93</v>
+      </c>
+      <c r="E246" s="64">
+        <v>91225.36</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B247">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C247">
+        <is>
+          <t xml:space="preserve">Kab. Ketapang</t>
+        </is>
+      </c>
+      <c r="D247" s="66">
+        <v>295.05</v>
+      </c>
+      <c r="E247" s="64">
+        <v>107693.92</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B248">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C248">
+        <is>
+          <t xml:space="preserve">Kab. Sintang</t>
+        </is>
+      </c>
+      <c r="D248" s="66">
+        <v>354.22</v>
+      </c>
+      <c r="E248" s="64">
+        <v>129290.13</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B249">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C249">
+        <is>
+          <t xml:space="preserve">Kab. Kapuas Hulu</t>
+        </is>
+      </c>
+      <c r="D249" s="66">
+        <v>134.42</v>
+      </c>
+      <c r="E249" s="64">
+        <v>49063.30</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B250">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C250">
+        <is>
+          <t xml:space="preserve">Kab. Bengkayang</t>
+        </is>
+      </c>
+      <c r="D250" s="66">
+        <v>118.74</v>
+      </c>
+      <c r="E250" s="64">
+        <v>43340.83</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B251">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C251">
+        <is>
+          <t xml:space="preserve">Kab. Landak</t>
+        </is>
+      </c>
+      <c r="D251" s="66">
+        <v>163.83</v>
+      </c>
+      <c r="E251" s="64">
+        <v>59797.95</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B252">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C252">
+        <is>
+          <t xml:space="preserve">Kab. Sekadau</t>
+        </is>
+      </c>
+      <c r="D252" s="66">
+        <v>88.53</v>
+      </c>
+      <c r="E252" s="64">
+        <v>32314.62</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B253">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C253">
+        <is>
+          <t xml:space="preserve">Kab. Melawi</t>
+        </is>
+      </c>
+      <c r="D253" s="66">
+        <v>85.33</v>
+      </c>
+      <c r="E253" s="64">
+        <v>31145.01</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B254">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C254">
+        <is>
+          <t xml:space="preserve">Kab. Kayong Utara</t>
+        </is>
+      </c>
+      <c r="D254" s="66">
+        <v>65.55</v>
+      </c>
+      <c r="E254" s="64">
+        <v>23926.48</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B255">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C255">
+        <is>
+          <t xml:space="preserve">Kab. Kubu Raya</t>
+        </is>
+      </c>
+      <c r="D255" s="66">
+        <v>434.09</v>
+      </c>
+      <c r="E255" s="64">
+        <v>158442.19</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B256">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C256">
+        <is>
+          <t xml:space="preserve">Kota Pontianak</t>
+        </is>
+      </c>
+      <c r="D256" s="66">
+        <v>441.88</v>
+      </c>
+      <c r="E256" s="64">
+        <v>161286.82</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B257">
+        <is>
+          <t xml:space="preserve">Kalimantan Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C257">
+        <is>
+          <t xml:space="preserve">Kota Singkawang</t>
+        </is>
+      </c>
+      <c r="D257" s="66">
+        <v>95.38</v>
+      </c>
+      <c r="E257" s="64">
+        <v>34813.50</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B258">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C258">
+        <is>
+          <t xml:space="preserve">Kab. Kotawaringin Barat</t>
+        </is>
+      </c>
+      <c r="D258" s="66">
+        <v>137.47</v>
+      </c>
+      <c r="E258" s="64">
+        <v>50175.64</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B259">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C259">
+        <is>
+          <t xml:space="preserve">Kab. Kotawaringin Timur</t>
+        </is>
+      </c>
+      <c r="D259" s="66">
+        <v>237.97</v>
+      </c>
+      <c r="E259" s="64">
+        <v>86858.62</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B260">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C260">
+        <is>
+          <t xml:space="preserve">Kab. Kapuas</t>
+        </is>
+      </c>
+      <c r="D260" s="66">
+        <v>213.72</v>
+      </c>
+      <c r="E260" s="64">
+        <v>78008.17</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B261">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C261">
+        <is>
+          <t xml:space="preserve">Kab. Barito Selatan</t>
+        </is>
+      </c>
+      <c r="D261" s="66">
+        <v>66.96</v>
+      </c>
+      <c r="E261" s="64">
+        <v>24439.67</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B262">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C262">
+        <is>
+          <t xml:space="preserve">Kab. Barito Utara</t>
+        </is>
+      </c>
+      <c r="D262" s="66">
+        <v>65.30</v>
+      </c>
+      <c r="E262" s="64">
+        <v>23833.48</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B263">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C263">
+        <is>
+          <t xml:space="preserve">Kab. Katingan</t>
+        </is>
+      </c>
+      <c r="D263" s="66">
+        <v>65.60</v>
+      </c>
+      <c r="E263" s="64">
+        <v>23942.39</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B264">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C264">
+        <is>
+          <t xml:space="preserve">Kab. Seruyan</t>
+        </is>
+      </c>
+      <c r="D264" s="66">
+        <v>83.04</v>
+      </c>
+      <c r="E264" s="64">
+        <v>30308.14</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B265">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C265">
+        <is>
+          <t xml:space="preserve">Kab. Sukamara</t>
+        </is>
+      </c>
+      <c r="D265" s="66">
+        <v>25.22</v>
+      </c>
+      <c r="E265" s="64">
+        <v>9203.69</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B266">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C266">
+        <is>
+          <t xml:space="preserve">Kab. Gunung Mas</t>
+        </is>
+      </c>
+      <c r="D266" s="66">
+        <v>98.38</v>
+      </c>
+      <c r="E266" s="64">
+        <v>35908.88</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B267">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C267">
+        <is>
+          <t xml:space="preserve">Kab. Pulang Pisau</t>
+        </is>
+      </c>
+      <c r="D267" s="66">
+        <v>68.11</v>
+      </c>
+      <c r="E267" s="64">
+        <v>24860.33</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B268">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C268">
+        <is>
+          <t xml:space="preserve">Kab. Murung Raya</t>
+        </is>
+      </c>
+      <c r="D268" s="66">
+        <v>57.08</v>
+      </c>
+      <c r="E268" s="64">
+        <v>20835.48</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B269">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C269">
+        <is>
+          <t xml:space="preserve">Kab. Barito Timur</t>
+        </is>
+      </c>
+      <c r="D269" s="66">
+        <v>46.16</v>
+      </c>
+      <c r="E269" s="64">
+        <v>16849.28</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B270">
+        <is>
+          <t xml:space="preserve">Kalimantan Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C270">
+        <is>
+          <t xml:space="preserve">Kota Palangkaraya</t>
+        </is>
+      </c>
+      <c r="D270" s="66">
+        <v>156.01</v>
+      </c>
+      <c r="E270" s="64">
+        <v>56945.11</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B271">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C271">
+        <is>
+          <t xml:space="preserve">Kab. Kotabaru</t>
+        </is>
+      </c>
+      <c r="D271" s="66">
+        <v>183.79</v>
+      </c>
+      <c r="E271" s="64">
+        <v>67082.22</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B272">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C272">
+        <is>
+          <t xml:space="preserve">Kab. Banjar</t>
+        </is>
+      </c>
+      <c r="D272" s="66">
+        <v>362.56</v>
+      </c>
+      <c r="E272" s="64">
+        <v>132335.31</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B273">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C273">
+        <is>
+          <t xml:space="preserve">Kab. Barito Kuala</t>
+        </is>
+      </c>
+      <c r="D273" s="66">
+        <v>98.80</v>
+      </c>
+      <c r="E273" s="64">
+        <v>36061.31</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B274">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C274">
+        <is>
+          <t xml:space="preserve">Kab. Tapin</t>
+        </is>
+      </c>
+      <c r="D274" s="66">
+        <v>83.74</v>
+      </c>
+      <c r="E274" s="64">
+        <v>30566.12</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B275">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C275">
+        <is>
+          <t xml:space="preserve">Kab. Hulu Sungai Selatan</t>
+        </is>
+      </c>
+      <c r="D275" s="66">
+        <v>97.28</v>
+      </c>
+      <c r="E275" s="64">
+        <v>35506.76</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B276">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C276">
+        <is>
+          <t xml:space="preserve">Kab. Hulu Sungai Tengah</t>
+        </is>
+      </c>
+      <c r="D276" s="66">
+        <v>105.22</v>
+      </c>
+      <c r="E276" s="64">
+        <v>38406.91</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B277">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C277">
+        <is>
+          <t xml:space="preserve">Kab. Hulu Sungai Utara</t>
+        </is>
+      </c>
+      <c r="D277" s="66">
+        <v>92.89</v>
+      </c>
+      <c r="E277" s="64">
+        <v>33905.00</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B278">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C278">
+        <is>
+          <t xml:space="preserve">Kab. Tabalong</t>
+        </is>
+      </c>
+      <c r="D278" s="66">
+        <v>117.61</v>
+      </c>
+      <c r="E278" s="64">
+        <v>42926.74</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B279">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C279">
+        <is>
+          <t xml:space="preserve">Kab. Tanah Bumbu</t>
+        </is>
+      </c>
+      <c r="D279" s="66">
+        <v>171.87</v>
+      </c>
+      <c r="E279" s="64">
+        <v>62732.73</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B280">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C280">
+        <is>
+          <t xml:space="preserve">Kab. Balangan</t>
+        </is>
+      </c>
+      <c r="D280" s="66">
+        <v>58.02</v>
+      </c>
+      <c r="E280" s="64">
+        <v>21178.29</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B281">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C281">
+        <is>
+          <t xml:space="preserve">Kota Banjarmasin</t>
+        </is>
+      </c>
+      <c r="D281" s="66">
+        <v>466.51</v>
+      </c>
+      <c r="E281" s="64">
+        <v>170275.42</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B282">
+        <is>
+          <t xml:space="preserve">Kalimantan Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C282">
+        <is>
+          <t xml:space="preserve">Kota Banjarbaru</t>
+        </is>
+      </c>
+      <c r="D282" s="66">
+        <v>185.90</v>
+      </c>
+      <c r="E282" s="64">
+        <v>67854.41</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B283">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C283">
+        <is>
+          <t xml:space="preserve">Kab. Paser</t>
+        </is>
+      </c>
+      <c r="D283" s="66">
+        <v>121.37</v>
+      </c>
+      <c r="E283" s="64">
+        <v>44299.90</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B284">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C284">
+        <is>
+          <t xml:space="preserve">Kab. Kutai Kartanegara</t>
+        </is>
+      </c>
+      <c r="D284" s="66">
+        <v>320.88</v>
+      </c>
+      <c r="E284" s="64">
+        <v>117121.18</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B285">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C285">
+        <is>
+          <t xml:space="preserve">Kab. Berau</t>
+        </is>
+      </c>
+      <c r="D285" s="66">
+        <v>140.50</v>
+      </c>
+      <c r="E285" s="64">
+        <v>51282.14</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B286">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C286">
+        <is>
+          <t xml:space="preserve">Kab. Kutai Barat</t>
+        </is>
+      </c>
+      <c r="D286" s="66">
+        <v>70.80</v>
+      </c>
+      <c r="E286" s="64">
+        <v>25843.02</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B287">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C287">
+        <is>
+          <t xml:space="preserve">Kab. Kutai Timur</t>
+        </is>
+      </c>
+      <c r="D287" s="66">
+        <v>212.89</v>
+      </c>
+      <c r="E287" s="64">
+        <v>77706.13</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B288">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C288">
+        <is>
+          <t xml:space="preserve">Kab. Penajam Paser Utara</t>
+        </is>
+      </c>
+      <c r="D288" s="66">
+        <v>98.28</v>
+      </c>
+      <c r="E288" s="64">
+        <v>35873.30</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B289">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C289">
+        <is>
+          <t xml:space="preserve">Kab. Mahakam Ulu</t>
+        </is>
+      </c>
+      <c r="D289" s="66">
+        <v>17.91</v>
+      </c>
+      <c r="E289" s="64">
+        <v>6538.11</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B290">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C290">
+        <is>
+          <t xml:space="preserve">Kota Balikpapan</t>
+        </is>
+      </c>
+      <c r="D290" s="66">
+        <v>528.87</v>
+      </c>
+      <c r="E290" s="64">
+        <v>193038.43</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B291">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C291">
+        <is>
+          <t xml:space="preserve">Kota Samarinda</t>
+        </is>
+      </c>
+      <c r="D291" s="66">
+        <v>599.45</v>
+      </c>
+      <c r="E291" s="64">
+        <v>218799.98</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B292">
+        <is>
+          <t xml:space="preserve">Kalimantan Timur</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C292">
+        <is>
+          <t xml:space="preserve">Kota Bontang</t>
+        </is>
+      </c>
+      <c r="D292" s="66">
+        <v>106.38</v>
+      </c>
+      <c r="E292" s="64">
+        <v>38829.46</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B293">
+        <is>
+          <t xml:space="preserve">Kalimantan Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C293">
+        <is>
+          <t xml:space="preserve">Kab. Bulungan</t>
+        </is>
+      </c>
+      <c r="D293" s="66">
+        <v>116.74</v>
+      </c>
+      <c r="E293" s="64">
+        <v>42611.01</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B294">
+        <is>
+          <t xml:space="preserve">Kalimantan Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C294">
+        <is>
+          <t xml:space="preserve">Kab. Nunukan</t>
+        </is>
+      </c>
+      <c r="D294" s="66">
+        <v>43.74</v>
+      </c>
+      <c r="E294" s="64">
+        <v>15966.42</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B295">
+        <is>
+          <t xml:space="preserve">Kalimantan Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C295">
+        <is>
+          <t xml:space="preserve">Kab. Tana Tidung</t>
+        </is>
+      </c>
+      <c r="D295" s="66">
+        <v>14.34</v>
+      </c>
+      <c r="E295" s="64">
+        <v>5234.83</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B296">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C296">
+        <is>
+          <t xml:space="preserve">Kab. Bolaang Mongondow</t>
+        </is>
+      </c>
+      <c r="D296" s="66">
+        <v>126.32</v>
+      </c>
+      <c r="E296" s="64">
+        <v>46108.26</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B297">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C297">
+        <is>
+          <t xml:space="preserve">Kab. Minahasa</t>
+        </is>
+      </c>
+      <c r="D297" s="66">
+        <v>175.13</v>
+      </c>
+      <c r="E297" s="64">
+        <v>63922.63</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B298">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C298">
+        <is>
+          <t xml:space="preserve">Kab. Kepulauan Sangihe</t>
+        </is>
+      </c>
+      <c r="D298" s="66">
+        <v>65.88</v>
+      </c>
+      <c r="E298" s="64">
+        <v>24045.31</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B299">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C299">
+        <is>
+          <t xml:space="preserve">Kab. Kepulauan Talaud</t>
+        </is>
+      </c>
+      <c r="D299" s="66">
+        <v>39.04</v>
+      </c>
+      <c r="E299" s="64">
+        <v>14250.18</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B300">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C300">
+        <is>
+          <t xml:space="preserve">Kab. Minahasa Selatan</t>
+        </is>
+      </c>
+      <c r="D300" s="66">
+        <v>96.01</v>
+      </c>
+      <c r="E300" s="64">
+        <v>35042.92</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B301">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C301">
+        <is>
+          <t xml:space="preserve">Kab. Minahasa Utara</t>
+        </is>
+      </c>
+      <c r="D301" s="66">
+        <v>120.48</v>
+      </c>
+      <c r="E301" s="64">
+        <v>43976.48</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B302">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C302">
+        <is>
+          <t xml:space="preserve">Kab. Minahasa Tenggara</t>
+        </is>
+      </c>
+      <c r="D302" s="66">
+        <v>46.92</v>
+      </c>
+      <c r="E302" s="64">
+        <v>17127.26</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B303">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C303">
+        <is>
+          <t xml:space="preserve">Kab. Bolaang Mongondow Utara</t>
+        </is>
+      </c>
+      <c r="D303" s="66">
+        <v>33.82</v>
+      </c>
+      <c r="E303" s="64">
+        <v>12343.28</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B304">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C304">
+        <is>
+          <t xml:space="preserve">Kab. Kep. Siau Tagulandang Biaro</t>
+        </is>
+      </c>
+      <c r="D304" s="66">
+        <v>28.85</v>
+      </c>
+      <c r="E304" s="64">
+        <v>10530.40</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B305">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C305">
+        <is>
+          <t xml:space="preserve">Kab. Bolaang Mongondow Selatan</t>
+        </is>
+      </c>
+      <c r="D305" s="66">
+        <v>29.06</v>
+      </c>
+      <c r="E305" s="64">
+        <v>10608.36</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B306">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C306">
+        <is>
+          <t xml:space="preserve">Kota Manado</t>
+        </is>
+      </c>
+      <c r="D306" s="66">
+        <v>291.20</v>
+      </c>
+      <c r="E306" s="64">
+        <v>106288.37</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B307">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C307">
+        <is>
+          <t xml:space="preserve">Kota Bitung</t>
+        </is>
+      </c>
+      <c r="D307" s="66">
+        <v>159.06</v>
+      </c>
+      <c r="E307" s="64">
+        <v>58055.22</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B308">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C308">
+        <is>
+          <t xml:space="preserve">Kota Tomohon</t>
+        </is>
+      </c>
+      <c r="D308" s="66">
+        <v>51.36</v>
+      </c>
+      <c r="E308" s="64">
+        <v>18747.13</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B309">
+        <is>
+          <t xml:space="preserve">Sulawesi Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C309">
+        <is>
+          <t xml:space="preserve">Kota Kotamobagu</t>
+        </is>
+      </c>
+      <c r="D309" s="66">
+        <v>86.74</v>
+      </c>
+      <c r="E309" s="64">
+        <v>31661.05</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B310">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C310">
+        <is>
+          <t xml:space="preserve">Kab. Banggai</t>
+        </is>
+      </c>
+      <c r="D310" s="66">
+        <v>183.11</v>
+      </c>
+      <c r="E310" s="64">
+        <v>66835.88</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B311">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C311">
+        <is>
+          <t xml:space="preserve">Kab. Buol</t>
+        </is>
+      </c>
+      <c r="D311" s="66">
+        <v>60.21</v>
+      </c>
+      <c r="E311" s="64">
+        <v>21976.65</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B312">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C312">
+        <is>
+          <t xml:space="preserve">Kab. Morowali</t>
+        </is>
+      </c>
+      <c r="D312" s="66">
+        <v>88.12</v>
+      </c>
+      <c r="E312" s="64">
+        <v>32164.53</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B313">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C313">
+        <is>
+          <t xml:space="preserve">Kab. Banggai Kepulauan</t>
+        </is>
+      </c>
+      <c r="D313" s="66">
+        <v>60.84</v>
+      </c>
+      <c r="E313" s="64">
+        <v>22207.33</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B314">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C314">
+        <is>
+          <t xml:space="preserve">Kab. Parigi Moutong</t>
+        </is>
+      </c>
+      <c r="D314" s="66">
+        <v>227.25</v>
+      </c>
+      <c r="E314" s="64">
+        <v>82947.89</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B315">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C315">
+        <is>
+          <t xml:space="preserve">Kab. Sigi</t>
+        </is>
+      </c>
+      <c r="D315" s="66">
+        <v>131.05</v>
+      </c>
+      <c r="E315" s="64">
+        <v>47833.43</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B316">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C316">
+        <is>
+          <t xml:space="preserve">Kab. Banggai Laut</t>
+        </is>
+      </c>
+      <c r="D316" s="66">
+        <v>37.46</v>
+      </c>
+      <c r="E316" s="64">
+        <v>13672.90</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B317">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C317">
+        <is>
+          <t xml:space="preserve">Kab. Morowali Utara</t>
+        </is>
+      </c>
+      <c r="D317" s="66">
+        <v>72.84</v>
+      </c>
+      <c r="E317" s="64">
+        <v>26587.70</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B318">
+        <is>
+          <t xml:space="preserve">Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C318">
+        <is>
+          <t xml:space="preserve">Kota Palu</t>
+        </is>
+      </c>
+      <c r="D318" s="66">
+        <v>193.75</v>
+      </c>
+      <c r="E318" s="64">
+        <v>70717.47</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B319">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C319">
+        <is>
+          <t xml:space="preserve">Kab. Kepulauan Selayar</t>
+        </is>
+      </c>
+      <c r="D319" s="66">
+        <v>56.35</v>
+      </c>
+      <c r="E319" s="64">
+        <v>20568.63</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B320">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C320">
+        <is>
+          <t xml:space="preserve">Kab. Bulukumba</t>
+        </is>
+      </c>
+      <c r="D320" s="66">
+        <v>182.50</v>
+      </c>
+      <c r="E320" s="64">
+        <v>66610.75</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B321">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C321">
+        <is>
+          <t xml:space="preserve">Kab. Bantaeng</t>
+        </is>
+      </c>
+      <c r="D321" s="66">
+        <v>83.23</v>
+      </c>
+      <c r="E321" s="64">
+        <v>30377.78</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B322">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C322">
+        <is>
+          <t xml:space="preserve">Kab. Jeneponto</t>
+        </is>
+      </c>
+      <c r="D322" s="66">
+        <v>166.18</v>
+      </c>
+      <c r="E322" s="64">
+        <v>60657.45</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B323">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C323">
+        <is>
+          <t xml:space="preserve">Kab. Takalar</t>
+        </is>
+      </c>
+      <c r="D323" s="66">
+        <v>130.42</v>
+      </c>
+      <c r="E323" s="64">
+        <v>47602.42</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B324">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C324">
+        <is>
+          <t xml:space="preserve">Kab. Gowa</t>
+        </is>
+      </c>
+      <c r="D324" s="66">
+        <v>400.00</v>
+      </c>
+      <c r="E324" s="64">
+        <v>145999.82</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B325">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C325">
+        <is>
+          <t xml:space="preserve">Kab. Sinjai</t>
+        </is>
+      </c>
+      <c r="D325" s="66">
+        <v>109.42</v>
+      </c>
+      <c r="E325" s="64">
+        <v>39939.61</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B326">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C326">
+        <is>
+          <t xml:space="preserve">Kab. Bone</t>
+        </is>
+      </c>
+      <c r="D326" s="66">
+        <v>407.59</v>
+      </c>
+      <c r="E326" s="64">
+        <v>148771.81</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B327">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C327">
+        <is>
+          <t xml:space="preserve">Kab. Maros</t>
+        </is>
+      </c>
+      <c r="D327" s="66">
+        <v>164.28</v>
+      </c>
+      <c r="E327" s="64">
+        <v>59962.05</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B328">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C328">
+        <is>
+          <t xml:space="preserve">Kab. Pangkajene dan Kepulauan</t>
+        </is>
+      </c>
+      <c r="D328" s="66">
+        <v>142.00</v>
+      </c>
+      <c r="E328" s="64">
+        <v>51830.44</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B329">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C329">
+        <is>
+          <t xml:space="preserve">Kab. Barru</t>
+        </is>
+      </c>
+      <c r="D329" s="66">
+        <v>77.82</v>
+      </c>
+      <c r="E329" s="64">
+        <v>28403.28</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B330">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C330">
+        <is>
+          <t xml:space="preserve">Kab. Soppeng</t>
+        </is>
+      </c>
+      <c r="D330" s="66">
+        <v>94.42</v>
+      </c>
+      <c r="E330" s="64">
+        <v>34463.15</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B331">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C331">
+        <is>
+          <t xml:space="preserve">Kab. Wajo</t>
+        </is>
+      </c>
+      <c r="D331" s="66">
+        <v>163.09</v>
+      </c>
+      <c r="E331" s="64">
+        <v>59528.58</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B332">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C332">
+        <is>
+          <t xml:space="preserve">Kab. Sidenreng Rappang</t>
+        </is>
+      </c>
+      <c r="D332" s="66">
+        <v>130.97</v>
+      </c>
+      <c r="E332" s="64">
+        <v>47802.74</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B333">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C333">
+        <is>
+          <t xml:space="preserve">Kab. Pinrang</t>
+        </is>
+      </c>
+      <c r="D333" s="66">
+        <v>184.05</v>
+      </c>
+      <c r="E333" s="64">
+        <v>67178.98</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B334">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C334">
+        <is>
+          <t xml:space="preserve">Kab. Enrekang</t>
+        </is>
+      </c>
+      <c r="D334" s="66">
+        <v>104.09</v>
+      </c>
+      <c r="E334" s="64">
+        <v>37991.19</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B335">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C335">
+        <is>
+          <t xml:space="preserve">Kab. Tana Toraja</t>
+        </is>
+      </c>
+      <c r="D335" s="66">
+        <v>108.39</v>
+      </c>
+      <c r="E335" s="64">
+        <v>39563.66</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B336">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C336">
+        <is>
+          <t xml:space="preserve">Kab. Luwu Utara</t>
+        </is>
+      </c>
+      <c r="D336" s="66">
+        <v>165.29</v>
+      </c>
+      <c r="E336" s="64">
+        <v>60330.12</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B337">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C337">
+        <is>
+          <t xml:space="preserve">Kab. Luwu Timur</t>
+        </is>
+      </c>
+      <c r="D337" s="66">
+        <v>122.21</v>
+      </c>
+      <c r="E337" s="64">
+        <v>44606.07</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B338">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C338">
+        <is>
+          <t xml:space="preserve">Kab. Toraja Utara</t>
+        </is>
+      </c>
+      <c r="D338" s="66">
+        <v>136.14</v>
+      </c>
+      <c r="E338" s="64">
+        <v>49692.20</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B339">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C339">
+        <is>
+          <t xml:space="preserve">Kota Makassar</t>
+        </is>
+      </c>
+      <c r="D339" s="64">
+        <v>1032.08</v>
+      </c>
+      <c r="E339" s="64">
+        <v>376707.41</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B340">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C340">
+        <is>
+          <t xml:space="preserve">Kota Parepare</t>
+        </is>
+      </c>
+      <c r="D340" s="66">
+        <v>79.33</v>
+      </c>
+      <c r="E340" s="64">
+        <v>28956.73</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B341">
+        <is>
+          <t xml:space="preserve">Sulawesi Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C341">
+        <is>
+          <t xml:space="preserve">Kota Palopo</t>
+        </is>
+      </c>
+      <c r="D341" s="66">
+        <v>95.43</v>
+      </c>
+      <c r="E341" s="64">
+        <v>34833.23</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B342">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C342">
+        <is>
+          <t xml:space="preserve">Kab. Kolaka</t>
+        </is>
+      </c>
+      <c r="D342" s="66">
+        <v>121.36</v>
+      </c>
+      <c r="E342" s="64">
+        <v>44297.57</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B343">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C343">
+        <is>
+          <t xml:space="preserve">Kab. Konawe</t>
+        </is>
+      </c>
+      <c r="D343" s="66">
+        <v>106.52</v>
+      </c>
+      <c r="E343" s="64">
+        <v>38879.65</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B344">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C344">
+        <is>
+          <t xml:space="preserve">Kab. Muna</t>
+        </is>
+      </c>
+      <c r="D344" s="66">
+        <v>94.11</v>
+      </c>
+      <c r="E344" s="64">
+        <v>34351.61</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B345">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C345">
+        <is>
+          <t xml:space="preserve">Kab. Buton</t>
+        </is>
+      </c>
+      <c r="D345" s="66">
+        <v>41.44</v>
+      </c>
+      <c r="E345" s="64">
+        <v>15125.75</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B346">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C346">
+        <is>
+          <t xml:space="preserve">Kab. Konawe Selatan</t>
+        </is>
+      </c>
+      <c r="D346" s="66">
+        <v>161.47</v>
+      </c>
+      <c r="E346" s="64">
+        <v>58937.65</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B347">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C347">
+        <is>
+          <t xml:space="preserve">Kab. Wakatobi</t>
+        </is>
+      </c>
+      <c r="D347" s="66">
+        <v>82.34</v>
+      </c>
+      <c r="E347" s="64">
+        <v>30054.47</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B348">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C348">
+        <is>
+          <t xml:space="preserve">Kab. Kolaka Utara</t>
+        </is>
+      </c>
+      <c r="D348" s="66">
+        <v>56.46</v>
+      </c>
+      <c r="E348" s="64">
+        <v>20608.05</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B349">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C349">
+        <is>
+          <t xml:space="preserve">Kab. Konawe Utara</t>
+        </is>
+      </c>
+      <c r="D349" s="66">
+        <v>28.13</v>
+      </c>
+      <c r="E349" s="64">
+        <v>10265.84</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B350">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C350">
+        <is>
+          <t xml:space="preserve">Kab. Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="D350" s="66">
+        <v>56.58</v>
+      </c>
+      <c r="E350" s="64">
+        <v>20651.85</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B351">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C351">
+        <is>
+          <t xml:space="preserve">Kab. Muna Barat</t>
+        </is>
+      </c>
+      <c r="D351" s="66">
+        <v>35.71</v>
+      </c>
+      <c r="E351" s="64">
+        <v>13035.61</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B352">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C352">
+        <is>
+          <t xml:space="preserve">Kab. Buton Tengah</t>
+        </is>
+      </c>
+      <c r="D352" s="66">
+        <v>60.14</v>
+      </c>
+      <c r="E352" s="64">
+        <v>21952.01</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B353">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C353">
+        <is>
+          <t xml:space="preserve">Kab. Buton Selatan</t>
+        </is>
+      </c>
+      <c r="D353" s="66">
+        <v>23.36</v>
+      </c>
+      <c r="E353" s="64">
+        <v>8527.64</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B354">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C354">
+        <is>
+          <t xml:space="preserve">Kota Kendari</t>
+        </is>
+      </c>
+      <c r="D354" s="66">
+        <v>242.25</v>
+      </c>
+      <c r="E354" s="64">
+        <v>88420.76</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B355">
+        <is>
+          <t xml:space="preserve">Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C355">
+        <is>
+          <t xml:space="preserve">Kota Bau Bau</t>
+        </is>
+      </c>
+      <c r="D355" s="66">
+        <v>90.00</v>
+      </c>
+      <c r="E355" s="64">
+        <v>32850.00</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B356">
+        <is>
+          <t xml:space="preserve">Gorontalo</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C356">
+        <is>
+          <t xml:space="preserve">Kab. Gorontalo</t>
+        </is>
+      </c>
+      <c r="D356" s="66">
+        <v>159.52</v>
+      </c>
+      <c r="E356" s="64">
+        <v>58224.95</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B357">
+        <is>
+          <t xml:space="preserve">Gorontalo</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C357">
+        <is>
+          <t xml:space="preserve">Kab. Bone Bolango</t>
+        </is>
+      </c>
+      <c r="D357" s="66">
+        <v>54.85</v>
+      </c>
+      <c r="E357" s="64">
+        <v>20018.79</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B358">
+        <is>
+          <t xml:space="preserve">Gorontalo</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C358">
+        <is>
+          <t xml:space="preserve">Kab. Pohuwato</t>
+        </is>
+      </c>
+      <c r="D358" s="66">
+        <v>59.97</v>
+      </c>
+      <c r="E358" s="64">
+        <v>21888.32</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B359">
+        <is>
+          <t xml:space="preserve">Gorontalo</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C359">
+        <is>
+          <t xml:space="preserve">Kota Gorontalo</t>
+        </is>
+      </c>
+      <c r="D359" s="66">
+        <v>142.24</v>
+      </c>
+      <c r="E359" s="64">
+        <v>51918.88</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B360">
+        <is>
+          <t xml:space="preserve">Sulawesi Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C360">
+        <is>
+          <t xml:space="preserve">Kab. Mamuju</t>
+        </is>
+      </c>
+      <c r="D360" s="66">
+        <v>142.81</v>
+      </c>
+      <c r="E360" s="64">
+        <v>52124.92</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B361">
+        <is>
+          <t xml:space="preserve">Sulawesi Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C361">
+        <is>
+          <t xml:space="preserve">Kab. Majene</t>
+        </is>
+      </c>
+      <c r="D361" s="66">
+        <v>70.96</v>
+      </c>
+      <c r="E361" s="64">
+        <v>25898.94</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B362">
+        <is>
+          <t xml:space="preserve">Sulawesi Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C362">
+        <is>
+          <t xml:space="preserve">Kab. Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="D362" s="66">
+        <v>56.01</v>
+      </c>
+      <c r="E362" s="64">
+        <v>20444.09</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B363">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C363">
+        <is>
+          <t xml:space="preserve">Kab. Maluku Tengah</t>
+        </is>
+      </c>
+      <c r="D363" s="66">
+        <v>151.21</v>
+      </c>
+      <c r="E363" s="64">
+        <v>55191.90</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B364">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C364">
+        <is>
+          <t xml:space="preserve">Kab. Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="D364" s="66">
+        <v>49.99</v>
+      </c>
+      <c r="E364" s="64">
+        <v>18245.33</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B365">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C365">
+        <is>
+          <t xml:space="preserve">Kab. Kepulauan Tanimbar</t>
+        </is>
+      </c>
+      <c r="D365" s="66">
+        <v>52.55</v>
+      </c>
+      <c r="E365" s="64">
+        <v>19179.73</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B366">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C366">
+        <is>
+          <t xml:space="preserve">Kab. Buru</t>
+        </is>
+      </c>
+      <c r="D366" s="66">
+        <v>60.03</v>
+      </c>
+      <c r="E366" s="64">
+        <v>21909.36</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B367">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C367">
+        <is>
+          <t xml:space="preserve">Kab. Seram Bagian Barat</t>
+        </is>
+      </c>
+      <c r="D367" s="66">
+        <v>85.99</v>
+      </c>
+      <c r="E367" s="64">
+        <v>31386.93</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B368">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C368">
+        <is>
+          <t xml:space="preserve">Kab. Kepulauan Aru</t>
+        </is>
+      </c>
+      <c r="D368" s="66">
+        <v>43.53</v>
+      </c>
+      <c r="E368" s="64">
+        <v>15889.76</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B369">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C369">
+        <is>
+          <t xml:space="preserve">Kota Ambon</t>
+        </is>
+      </c>
+      <c r="D369" s="66">
+        <v>246.74</v>
+      </c>
+      <c r="E369" s="64">
+        <v>90061.20</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B370">
+        <is>
+          <t xml:space="preserve">Maluku</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C370">
+        <is>
+          <t xml:space="preserve">Kota Tual</t>
+        </is>
+      </c>
+      <c r="D370" s="66">
+        <v>59.88</v>
+      </c>
+      <c r="E370" s="64">
+        <v>21857.51</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B371">
+        <is>
+          <t xml:space="preserve">Maluku Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C371">
+        <is>
+          <t xml:space="preserve">Kab. Halmahera Tengah</t>
+        </is>
+      </c>
+      <c r="D371" s="66">
+        <v>48.49</v>
+      </c>
+      <c r="E371" s="64">
+        <v>17698.30</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B372">
+        <is>
+          <t xml:space="preserve">Maluku Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C372">
+        <is>
+          <t xml:space="preserve">Kab. Halmahera Selatan</t>
+        </is>
+      </c>
+      <c r="D372" s="66">
+        <v>102.15</v>
+      </c>
+      <c r="E372" s="64">
+        <v>37286.06</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B373">
+        <is>
+          <t xml:space="preserve">Maluku Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C373">
+        <is>
+          <t xml:space="preserve">Kab. Kepulauan Sula</t>
+        </is>
+      </c>
+      <c r="D373" s="66">
+        <v>50.20</v>
+      </c>
+      <c r="E373" s="64">
+        <v>18321.36</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B374">
+        <is>
+          <t xml:space="preserve">Maluku Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C374">
+        <is>
+          <t xml:space="preserve">Kab. Halmahera Timur</t>
+        </is>
+      </c>
+      <c r="D374" s="66">
+        <v>53.84</v>
+      </c>
+      <c r="E374" s="64">
+        <v>19652.42</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B375">
+        <is>
+          <t xml:space="preserve">Maluku Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C375">
+        <is>
+          <t xml:space="preserve">Kab. Pulau Morotai</t>
+        </is>
+      </c>
+      <c r="D375" s="66">
+        <v>32.74</v>
+      </c>
+      <c r="E375" s="64">
+        <v>11951.56</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B376">
+        <is>
+          <t xml:space="preserve">Maluku Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C376">
+        <is>
+          <t xml:space="preserve">Kab. Pulau Taliabu</t>
+        </is>
+      </c>
+      <c r="D376" s="66">
+        <v>32.60</v>
+      </c>
+      <c r="E376" s="64">
+        <v>11900.46</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B377">
+        <is>
+          <t xml:space="preserve">Maluku Utara</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C377">
+        <is>
+          <t xml:space="preserve">Kota Tidore Kepulauan</t>
+        </is>
+      </c>
+      <c r="D377" s="66">
+        <v>47.45</v>
+      </c>
+      <c r="E377" s="64">
+        <v>17317.50</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B378">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C378">
+        <is>
+          <t xml:space="preserve">Kab. Jayapura</t>
+        </is>
+      </c>
+      <c r="D378" s="66">
+        <v>101.28</v>
+      </c>
+      <c r="E378" s="64">
+        <v>36967.38</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B379">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C379">
+        <is>
+          <t xml:space="preserve">Kab. Kepulauan Yapen</t>
+        </is>
+      </c>
+      <c r="D379" s="66">
+        <v>46.44</v>
+      </c>
+      <c r="E379" s="64">
+        <v>16951.62</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B380">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C380">
+        <is>
+          <t xml:space="preserve">Kab. Biak Numfor</t>
+        </is>
+      </c>
+      <c r="D380" s="66">
+        <v>58.72</v>
+      </c>
+      <c r="E380" s="64">
+        <v>21434.55</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B381">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C381">
+        <is>
+          <t xml:space="preserve">Kab. Sarmi</t>
+        </is>
+      </c>
+      <c r="D381" s="66">
+        <v>16.84</v>
+      </c>
+      <c r="E381" s="64">
+        <v>6146.60</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B382">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C382">
+        <is>
+          <t xml:space="preserve">Kab. Keerom</t>
+        </is>
+      </c>
+      <c r="D382" s="66">
+        <v>26.56</v>
+      </c>
+      <c r="E382" s="64">
+        <v>9694.55</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B383">
+        <is>
+          <t xml:space="preserve">Papua</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C383">
+        <is>
+          <t xml:space="preserve">Kota Jayapura</t>
+        </is>
+      </c>
+      <c r="D383" s="66">
+        <v>241.87</v>
+      </c>
+      <c r="E383" s="64">
+        <v>88282.84</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B384">
+        <is>
+          <t xml:space="preserve">Papua Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C384">
+        <is>
+          <t xml:space="preserve">Kab. Manokwari</t>
+        </is>
+      </c>
+      <c r="D384" s="66">
+        <v>180.41</v>
+      </c>
+      <c r="E384" s="64">
+        <v>65849.34</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B385">
+        <is>
+          <t xml:space="preserve">Papua Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C385">
+        <is>
+          <t xml:space="preserve">Kab. Fak Fak</t>
+        </is>
+      </c>
+      <c r="D385" s="66">
+        <v>35.55</v>
+      </c>
+      <c r="E385" s="64">
+        <v>12976.48</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B386">
+        <is>
+          <t xml:space="preserve">Papua Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C386">
+        <is>
+          <t xml:space="preserve">Kab. Teluk Wondama</t>
+        </is>
+      </c>
+      <c r="D386" s="66">
+        <v>17.50</v>
+      </c>
+      <c r="E386" s="64">
+        <v>6386.92</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B387">
+        <is>
+          <t xml:space="preserve">Papua Barat</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C387">
+        <is>
+          <t xml:space="preserve">Kab. Kaimana</t>
+        </is>
+      </c>
+      <c r="D387" s="66">
+        <v>25.71</v>
+      </c>
+      <c r="E387" s="64">
+        <v>9382.69</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B388">
+        <is>
+          <t xml:space="preserve">Papua Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C388">
+        <is>
+          <t xml:space="preserve">Kab. Boven Digoel</t>
+        </is>
+      </c>
+      <c r="D388" s="66">
+        <v>26.08</v>
+      </c>
+      <c r="E388" s="64">
+        <v>9518.18</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B389">
+        <is>
+          <t xml:space="preserve">Papua Selatan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C389">
+        <is>
+          <t xml:space="preserve">Kab. Asmat</t>
+        </is>
+      </c>
+      <c r="D389" s="66">
+        <v>46.48</v>
+      </c>
+      <c r="E389" s="64">
+        <v>16965.20</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B390">
+        <is>
+          <t xml:space="preserve">Papua Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C390">
+        <is>
+          <t xml:space="preserve">Kab. Mimika</t>
+        </is>
+      </c>
+      <c r="D390" s="66">
+        <v>156.51</v>
+      </c>
+      <c r="E390" s="64">
+        <v>57125.42</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B391">
+        <is>
+          <t xml:space="preserve">Papua Tengah</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C391">
+        <is>
+          <t xml:space="preserve">Kab. Dogiyai</t>
+        </is>
+      </c>
+      <c r="D391" s="66">
+        <v>47.13</v>
+      </c>
+      <c r="E391" s="64">
+        <v>17201.43</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B392">
+        <is>
+          <t xml:space="preserve">Papua Pegunungan</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C392">
+        <is>
+          <t xml:space="preserve">Kab. Jayawijaya</t>
+        </is>
+      </c>
+      <c r="D392" s="66">
+        <v>113.00</v>
+      </c>
+      <c r="E392" s="64">
+        <v>41244.56</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B393">
+        <is>
+          <t xml:space="preserve">Papua Barat Daya</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C393">
+        <is>
+          <t xml:space="preserve">Kab. Sorong</t>
+        </is>
+      </c>
+      <c r="D393" s="66">
+        <v>50.38</v>
+      </c>
+      <c r="E393" s="64">
+        <v>18388.55</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B394">
+        <is>
+          <t xml:space="preserve">Papua Barat Daya</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C394">
+        <is>
+          <t xml:space="preserve">Kab. Sorong Selatan</t>
+        </is>
+      </c>
+      <c r="D394" s="66">
+        <v>20.78</v>
+      </c>
+      <c r="E394" s="64">
+        <v>7586.31</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B395">
+        <is>
+          <t xml:space="preserve">Papua Barat Daya</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C395">
+        <is>
+          <t xml:space="preserve">Kab. Raja Ampat</t>
+        </is>
+      </c>
+      <c r="D395" s="66">
+        <v>27.11</v>
+      </c>
+      <c r="E395" s="64">
+        <v>9893.40</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="65">
+        <v>2023</v>
+      </c>
+      <c t="inlineStr" r="B396">
+        <is>
+          <t xml:space="preserve">Papua Barat Daya</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C396">
+        <is>
+          <t xml:space="preserve">Kota Sorong</t>
+        </is>
+      </c>
+      <c r="D396" s="66">
+        <v>147.49</v>
+      </c>
+      <c r="E396" s="64">
+        <v>53833.49</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
